--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11EF357A-428D-4D64-9937-F9B1EA670B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82590345-C4B9-4651-B808-B580B2BAE45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="30" windowWidth="37140" windowHeight="20475" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,10 +20,13 @@
     <sheet name="Input - Dairy" sheetId="70" r:id="rId5"/>
     <sheet name="3.3.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Dairy" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="104" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="108" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -104,6 +107,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title">_xlfn.LAMBDA("Emission factor for organic fertiliser and crop residues returned to the soil")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
@@ -495,7 +505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="255">
   <si>
     <t>Home</t>
   </si>
@@ -1333,6 +1343,12 @@
   </si>
   <si>
     <t>Litres of milk</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
   </si>
 </sst>
 </file>
@@ -2761,94 +2777,28 @@
     <cellStyle name="Variable type input" xfId="67" xr:uid="{8B650911-9251-4CA7-8D5F-FC6CA32FF621}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{B3E8C5CF-C085-4800-95E7-0E14E266DEDE}"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="94">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3689,6 +3639,96 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4784,20 +4824,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="92"/>
-      <tableStyleElement type="headerRow" dxfId="91"/>
-      <tableStyleElement type="totalRow" dxfId="90"/>
-      <tableStyleElement type="firstColumn" dxfId="89"/>
-      <tableStyleElement type="firstRowStripe" dxfId="88"/>
-      <tableStyleElement type="secondRowStripe" dxfId="87"/>
+      <tableStyleElement type="wholeTable" dxfId="93"/>
+      <tableStyleElement type="headerRow" dxfId="92"/>
+      <tableStyleElement type="totalRow" dxfId="91"/>
+      <tableStyleElement type="firstColumn" dxfId="90"/>
+      <tableStyleElement type="firstRowStripe" dxfId="89"/>
+      <tableStyleElement type="secondRowStripe" dxfId="88"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="totalRow" dxfId="84"/>
-      <tableStyleElement type="firstColumn" dxfId="83"/>
-      <tableStyleElement type="firstRowStripe" dxfId="82"/>
-      <tableStyleElement type="secondRowStripe" dxfId="81"/>
+      <tableStyleElement type="wholeTable" dxfId="87"/>
+      <tableStyleElement type="headerRow" dxfId="86"/>
+      <tableStyleElement type="totalRow" dxfId="85"/>
+      <tableStyleElement type="firstColumn" dxfId="84"/>
+      <tableStyleElement type="firstRowStripe" dxfId="83"/>
+      <tableStyleElement type="secondRowStripe" dxfId="82"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -9011,6 +9051,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -9083,7 +9143,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="80" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="81" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9101,13 +9161,13 @@
     <tableColumn id="1" xr3:uid="{8ACEF380-8A1A-411E-A23A-665A769E20C7}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9125,7 +9185,7 @@
     <tableColumn id="1" xr3:uid="{34872B36-E9B0-443E-A8EC-EC35C2572085}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9143,7 +9203,7 @@
     <tableColumn id="1" xr3:uid="{B2383F7B-29D1-4559-9E34-4E2C127CFB5C}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9163,13 +9223,13 @@
     <tableColumn id="1" xr3:uid="{A4A196FD-DBDB-46C0-83CE-7C77F2C477B3}" name="Area">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9188,10 +9248,10 @@
     <tableColumn id="1" xr3:uid="{D85FDEBC-2FC0-45F1-BCD6-4464E2C22E94}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9210,10 +9270,10 @@
     <tableColumn id="1" xr3:uid="{C1D0CE9E-4549-48D9-9C0F-1310FC73ABC5}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9222,20 +9282,20 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{903FF72D-5AA8-4D04-BC68-A876F0B27A90}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{99D087D3-C39C-4ECF-9296-8C2C5BE8EE1C}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7F794626-A850-4164-8339-B540B2DF4318}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{969F5BDD-487B-4F3E-ACA1-EFACD7C856E9}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DAE38D79-3412-44EE-B743-F7EA54525797}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{AF1BBA32-A027-4F49-8C27-67786F752701}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0A80F820-FBCF-4CD9-BB99-A505AD6A6475}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{0DB3791F-01DF-4F72-B38D-C4988C5A54A9}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9244,12 +9304,12 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{A467D148-4878-4FAD-BB3C-F97D06CA9512}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{34158F32-E265-4A59-AB6D-3DD119B51B2E}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{C82476DA-E731-4E10-9D5A-E9F0C1FC06BA}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{A2B9D84A-A0D3-4183-BBFA-F3315B63AD80}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9258,16 +9318,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{9914CD11-0EFE-4643-96AF-5AA68162B523}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8D379F3C-93FE-49D1-A9DC-243D77BD56FD}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{65D9E7F2-5AA3-4F6D-B872-299BD4277352}" name="Gas">
+    <tableColumn id="1" xr3:uid="{CBC8C518-F94B-428D-BD7A-9E5F6BC0BD6B}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E11C296-A27E-44C8-B866-B60D8484DA21}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{76E24D37-684F-4F17-AE5B-4D3AB58E9B09}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9276,7 +9336,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{39DEC118-7605-4D43-9B0E-4EC1C1188999}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{4677D3E3-B30E-466C-B39E-A8BED4CDEEA8}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9285,19 +9345,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{24DF9520-BD4A-4E94-BBCC-0D5B7E7A8E54}" name="Gas">
+    <tableColumn id="1" xr3:uid="{BCCDB05B-CC33-4FB9-9E7A-6150D67B2EEB}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{719EA7B0-E1E5-4B9A-9E3D-3FFF5967D16D}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{04D931B1-A05A-46B4-8DEF-CE9AB9A484DA}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF7D1800-FE1C-4287-A8AE-6903F6F799C1}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{B849BB12-2C5B-4627-BEC5-0BB60049DDD6}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EAFCE0E3-845A-46DD-9AB0-BABC1C0E7CFA}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{4E47D044-2D2D-4BEB-953C-3E76EF21381B}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4BEB747A-4ACF-4E38-AEBF-06ED8AF9CE76}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{05044F31-B483-4A96-AC48-D9508428B5D8}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9320,7 +9380,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{EBE267B3-46EA-4CA7-9B3C-1A1F54218027}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{B2F622CC-E107-46D4-B379-65E951FAD1E3}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9340,52 +9400,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{57B6CA81-618B-4698-9F97-AD28407946EB}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{D27ECB6B-999A-4BD3-B047-A5AAC859AEAF}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{01C1D4B8-FE13-46DA-BB59-A5008C6FE7C1}" name="MAT" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{AA6488F9-231D-4939-BDFA-B7CBED91888F}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{102A624F-AE25-4F8F-B3F0-59DB196609CC}" name="MAP" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{ADC6FD29-BC7C-4785-98DB-9C4A3BCEB1D0}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F989612B-CC72-45D5-AE66-26DF38DFC6EA}" name="Frost days per year" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{466645EB-B94B-4DF4-8EA0-096EA00E81FB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{01545F31-673F-4A04-A77E-2429EE93C858}" name="Elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{BE315AAD-BE19-47C8-AB5F-4B616B19F040}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{25F16A09-9A57-463B-9BCB-20875BB51C44}" name="MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DF314910-84DB-47B1-B381-B405E58B2391}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5AA65FCB-002B-47F1-A287-E218559BCF41}" name="Min temp" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{2FDF8B6B-762F-4F7C-BAD1-E14E0BEE7BB6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C0739D72-8114-41EC-AE17-F0842D7BE327}" name="Max temp" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{07863784-E03B-4255-B45B-3F0FDC32B807}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{838C2DB7-9885-4DD3-9B09-44688DEE8F3E}" name="Min rainfall" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{8A3A2332-0D79-4AF0-BFF9-195AC9D36A9B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{AC6CC6C2-C45B-4428-B2ED-43073BD9C77B}" name="Max rainfall" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1E8A1FA8-7602-40D4-9D62-C0743544DC8C}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D27C9106-4113-428E-A02E-BB79B2F36A53}" name="Min frost days" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{474010DE-FFE2-4FBE-837A-9ABC26E1FFA6}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2C7CD77E-0CE7-472B-80F9-ED09AE8A7629}" name="Max frost days" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{6222BDCD-C79D-473D-B3B9-61585F481A20}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{FAF6B10D-23FD-49F4-B389-A5D911DA4EB0}" name="Min elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{E30A3D94-830C-4D5F-9910-B32467D45A59}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C3D3CE5A-28C9-4BA8-9403-42CCEEFC311A}" name="Max elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{1C9BEB83-BFDD-4486-A2AF-1A8246AE2001}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{41AF1E4E-419B-49D3-B5DD-31A71A63AD52}" name="Min MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E9C2232B-89B7-4599-807F-84A1995BE780}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{0323E4F1-1C74-4A8C-A893-AA2777B9A8E5}" name="Max MAP:PET" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{B65144AE-98E9-4B77-A979-5D7E8FD05C90}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9394,16 +9454,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{E4CA1693-7EC0-48C3-8123-A6D663D828A8}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{F8875253-5CC5-4845-9C8E-854D56A6E3F0}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{49E074F6-1F46-427E-8A7B-BFEA18900DC4}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C264AE15-9D43-4230-8CF3-005ACA80737C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7FF83C7F-09C9-4F06-BECA-CDFF7F5BD9FB}" name="Wet or Dry Zone" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F6A705B5-3BB9-4F52-AE9B-8647BEFF7A17}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9412,7 +9472,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{18520BC8-5672-4822-908B-809C356B033A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{95C6C6F3-42C4-478B-8346-63E22AD7F87A}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9420,16 +9480,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{083149F2-73DE-4562-B91A-1F9C39334064}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{C7C6E4BE-3C22-45E4-A11F-84156B8A3DB9}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{14D1E32A-5A09-4329-8DC4-EAD6A0F58865}" name="MAT">
+    <tableColumn id="2" xr3:uid="{A48E5EA9-E6CE-4D72-B6E7-3FFE5BDA2E65}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C067EEEF-2F54-4838-949C-910BB29190EE}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{D7D52AD2-6F75-4510-AEC8-4EAD116F1CAF}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1A7E3D6B-ED50-49B2-8FFF-27C59B2D2298}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{4018D7D4-DF55-44A4-A0F2-6A5A4BCDAB87}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9438,7 +9498,7 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{1BCEE09E-35BE-4F5B-9886-18B04A28577F}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{51766D64-EB6A-4D38-A300-20E5731DD33D}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9446,16 +9506,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6419F08F-BAEF-4F99-9D31-2F07F0CBAEC1}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{219B8F52-B5EA-4032-8B6D-4D220111F85B}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C5E53696-D0AD-48E4-A387-F00098834B82}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{FD4A3A19-FF3D-400B-A8C8-A68F33F8F8DA}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AEB22F2A-45B7-4985-926A-90CE467ACCA3}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{DF5FCECE-AE20-4C0D-BFFD-52B5EBCF500E}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1E498886-42FD-468A-8875-3F9783E47004}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{70B09D42-B19F-4924-BAF7-D2F5DBEA0DF0}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9464,16 +9524,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1BDEC461-6A93-4A97-90E4-9A8AA40A19DB}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{C499DCAA-18C0-47FB-820F-1C75670123F0}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7479AB66-B537-45F0-95C3-F780F47F5E4D}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{EC899F97-ECBA-4F0E-A172-2EC8376E16E9}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7681297D-A0F0-4054-A87F-AE8E786F8B43}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{A5779332-5060-4201-8975-36DF50DA1602}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9482,16 +9542,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{21C81900-DCEC-41E8-B766-0A4CBD6AFDD7}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{01D758DC-4439-42E7-AC34-1E1F5A0F772D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1242AC1A-2AFA-428F-935B-83A73B49F1AF}" name="Data source">
+    <tableColumn id="1" xr3:uid="{FC07B152-4ED2-4190-B16C-BBF4FC9F363C}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A432E50B-9E0E-4A79-9E3B-C047686F9E56}" name="Data score">
+    <tableColumn id="2" xr3:uid="{859033F3-598E-4959-8D88-127300FC8D72}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9500,16 +9560,16 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{C3F08F2B-C3BE-4F58-9F6F-330BA0E52867}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F6F4B230-8E37-40DD-9E94-BC61E7E40F0B}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CA6CB252-C2A3-40D6-9473-9FC46E9D52A4}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{627D4BA3-08BB-4BFD-80C4-18A175949150}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{17B50AED-915B-4AAF-A792-B6C8FBF0C02A}" name="FracWET" dataDxfId="27">
+    <tableColumn id="2" xr3:uid="{21DB7D11-31D2-41AB-A91C-AB83B43E2E99}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9518,7 +9578,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{6AE7B8FB-16AF-416E-98A4-D699DD5C5E8A}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{CD9DD92F-8279-41CA-A21F-DD419B886E19}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9527,19 +9587,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9A1113FC-3C11-4120-8A7A-C6A066062811}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{AE40C6BA-74D3-4060-9775-3EB0568758BA}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{19F26070-D269-4461-9AA9-E73E9C3B4B2E}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{A910253C-FA98-4A1C-9476-3F1AAA731272}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{21B682C6-C2D0-424C-AD39-4F3E40D4636F}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{95BF6DA5-9C67-423C-801D-4D943EA26E64}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6962E14F-8525-41AD-A04F-63D56983CE42}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{B2B411F1-934F-4264-A685-88BBF75752D3}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3BE4975D-FE3A-45D5-891E-ED75504CC358}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{BC28A846-827F-49BE-8895-7AF07AC20232}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9548,16 +9608,16 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{A13CB41C-F794-4760-AC66-5B531D674B09}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{D129F0C6-DD37-4F92-A9FF-804A02D640C0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CAC3C0F9-1257-4074-B70D-B5E41C33E503}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{1CEC1953-8E56-4FD4-BC26-3865CAACC286}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{493CDD78-3DCB-49BC-B18C-971DBEBBEFAD}" name="FracWET" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3F42D44F-1CF8-49F4-81D0-03F6A55595DF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9566,16 +9626,16 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{4B66389F-5E7A-480C-811A-03404D9514DD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{3E4CDAAD-6977-4252-B238-B6746EE1D2D8}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6A630E68-DE8C-4AED-8D19-EEAAD9054DF8}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{E3913DC5-18BF-4429-B563-93C6A8F41687}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1BCF572D-EFF8-47B4-9A54-09684720C466}" name="EFPRP" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{84A849F0-4488-4D62-AD7E-B9EC4921BE0E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9596,16 +9656,16 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{F6508C63-E9E0-470A-9DC6-5393265238C6}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{F85EE619-A0C5-4C5C-9D4B-D2DB59E26245}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F3D2FAD8-2DF7-440E-9815-F9954FD522E7}" name="Month">
+    <tableColumn id="1" xr3:uid="{5BE0D823-5222-434D-9E2E-2F0E4EFE4D24}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E686A930-9FC6-45F2-A491-349E9B878124}" name="Season" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CAFE497D-DA77-442E-8064-29E27FA514E4}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9614,7 +9674,7 @@
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{DC651049-2627-4EC7-8E7F-25B154AFB6E0}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{0B86884D-E319-4505-86F6-43FE2BEEA592}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9634,52 +9694,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{42F53388-4525-4EB9-9628-BCBEA2F30578}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{B44084F6-B587-4CAE-8739-AC4B37EFE76F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{76933AB0-11DA-4292-8FE5-DE8E2CA4B88D}" name="MAT (ºC)" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4BDA08BD-756F-4B06-BAEC-1C98826106F0}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C76F11EA-A68F-4DDA-AB7D-A620B6EF4C44}" name="Anaerobic lagoon" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A7303D30-0C89-45D2-B4E1-EA0EF1649503}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2A59FC53-FA95-42F8-A803-83894C899534}" name="Digester / covered lagoons" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{C6E7430C-F8AE-4940-BB83-93D2E45DAF4D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{68317A95-2AB4-45D9-AACA-B1FFC6DCAD30}" name="Liquid systems" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FF1C7AF5-F58D-4463-857A-E226C8720E94}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{60C2DD5C-EF5D-46AB-A17D-EA174DBC06AB}" name="Daily spread" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4B0ACC6E-B49C-4D66-8D15-452C3D392828}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{13E6D90B-E8DC-4961-9A38-4984A6364EC3}" name="Composting (passive windrow)" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{73EDE90B-A287-40DA-BAB9-8974CE978C2F}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{485E7893-DB4C-4B24-975D-397921C40F6A}" name="Solid storage" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{EE40E181-A636-450F-B6D8-50AAA25151B7}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{35D07BA0-D24C-47DD-BCE9-8AEB94688BBD}" name="Pit storage" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{C3264EAA-7EED-4B15-84F6-E857933D554C}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8A8038AA-B56B-40E7-94C4-CFC40CEFAF7B}" name="Deep litter" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{ED6C1257-139D-4E34-B207-7A36AA4BD374}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D8FB6B0A-E569-4A66-B2B7-67E40B8006C7}" name="Poultry manure with bedding" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{FF40561E-7552-45AE-BD73-BD4FE67EFCBE}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9708DD5D-0DF4-4D67-BB71-ADF7EFD4F4DF}" name="Poultry manure without bedding" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6F8E8A90-DFE4-49D8-937A-D94686DE505C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{102B5F58-FFEC-4FFD-AC7E-15228F5CB463}" name="Direct processing" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{755860C4-2725-4DA6-8D53-0AF45AFD38DB}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{5D5FE3CD-8EA9-40AB-A6D2-55C163061365}" name="Direct application" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{0431DBA3-DB30-4D87-BEA7-2ACCE4C7A076}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{689C453B-2907-4AE7-80EF-A626BEEC7189}" name="Pasture range and paddock" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{FD82C3C0-5829-41E9-9B97-A0692E3C9093}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{600A278F-92FA-4925-ADAF-21269BA28878}" name="MAT raw" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C0CF46EB-58DB-48D5-9751-7E6B0D642CAB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9688,6 +9748,24 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{D36D9588-FBBA-47AF-B016-117A7CB4C015}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{6DFBEF8F-8540-41EE-B08C-9E7C56290E48}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{AF94C142-CC61-437C-87D9-52B720B134A8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D8:F26" totalsRowShown="0">
   <autoFilter ref="D8:F26" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -9721,13 +9799,13 @@
     <tableColumn id="1" xr3:uid="{CAC4C566-E7DF-44B3-BDB4-4B1785D5F9F0}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="79" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="80" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="78" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="79" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="77" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9746,10 +9824,10 @@
     <tableColumn id="1" xr3:uid="{40374F5E-9BC3-4080-A28F-8B1F65DE1774}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="76" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="75" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9770,16 +9848,16 @@
     <tableColumn id="1" xr3:uid="{69C0AC05-6C13-494A-8124-C36C4B6D01B6}" name="Milking cows">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="74" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="73" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="74" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="72" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="73" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="71" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="72" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9788,7 +9866,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="70" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="71" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D54:H55" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9818,7 +9896,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="69" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="70" dataCellStyle="Content normal">
   <autoFilter ref="D62:G64" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9826,16 +9904,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="68" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="69" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="67" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="68" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="66" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="67" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="65" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="66" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9861,31 +9939,31 @@
     <tableColumn id="1" xr3:uid="{A54F6170-CD83-454D-874A-2A78490F2BD1}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="64" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="65" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="63" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="64" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="60" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15043,47 +15121,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E10:M10 E24:M25 E28:M29 O43:P43 N44 J85:J90 K89:M89 K95:M95 F98 J101:J106 K105:M105 K110:M110 K114:M114 K123:M123">
-    <cfRule type="cellIs" dxfId="8" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="30" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:M15">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:M19">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36:M38">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:M43">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F88">
-    <cfRule type="cellIs" dxfId="3" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91">
-    <cfRule type="cellIs" dxfId="2" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:M67">
-    <cfRule type="cellIs" dxfId="1" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="24" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K70:M72">
-    <cfRule type="cellIs" dxfId="0" priority="23" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="23" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20164,8 +20242,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F831202-1887-4293-9408-079FA11C6DF6}">
-  <dimension ref="A1:BY250"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFDC5093-53DA-454A-9B4A-8C21A9DD752C}">
+  <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="7" customWidth="1"/>
@@ -21568,31 +21646,31 @@
       </c>
       <c r="T97" s="39"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="56" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="56" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="56" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="56" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="56" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="56" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="56"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="56"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -24078,10 +24156,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="6" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="56" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="E257" s="39" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="39" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="39" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="39" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="16">
+  <tableParts count="17">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -24098,6 +24228,7 @@
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24577,6 +24708,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABDAG8AdwBzACAAYQBuAGQAIABIAGUAaQBmAGUAcgBzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgAFwAdQAwADAAMgA3AFIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAXAB1ADAAMAAyADcARABhAGkAcgB5ACAAQQB1AHMAdAByAGEAbABpAGEAIABbADEAXQBcAHUAMAAwADIANwAgAGEAbgBkACAAaQBzACAAbgBvAHQAIAB1AHMAZQBkACAAaQBuACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAZABpAHUAbQAgAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADUANQAwACwAIAAzADgAMAAsACAAMQA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABhAHIAZwBlACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AbABzAHQAZQBpAG4ALQBGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADUAMAAsACAANAA1ADAALAAgADEAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBpAGUAcwBpAGEAbgAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANQAwADAALAAgADMANQAwACwAIAAxADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQBcACIALAAgADQAMAAwACwAIAAyADcANQAsACAAMQAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBlAHIAcwBlAHkAIABjAHIAbwBzAHMAYgByAGUAZABcACIALAAgADQANQAwACwAIAAzADEANQAsACAAMQAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB5AHIAcwBoAGkAcgBlAFwAIgAsACAANQA0ADAALAAgADMANwA1ACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHUAZQByAG4AcwBlAHkAXAAiACwAIAA0ADgAMAAsACAAMwAzADUALAAgADEANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBvAHcAbgAgAFMAdwBpAHMAcwBcACIALAAgADYAMAAwACwAIAA0ADEANQAsACAAMQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBsAGwAYQB3AGEAcgByAGEALwBBAHUAcwBzAGkAZQAgAFIAZQBkAFwAIgAsACAANQA1ADAALAAgADMANwA1ACwAIAAxADUAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEIAdQBsAGwAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgADUAOQAwACwAIAA1ADkAMAAsACAANQA5ADAALAAgADcANwAwACwAIAA3ADcAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAagA9ADMALAA1ADsAIABOAFAAVwBqAD0AMwAsADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAAoAFYAUwBqAD0AMwAsADUAKQBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIABFAHgAYwByAGUAdABlAGQAIAAoAE4AUABXAGoAPQAzACwANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMQA3ADYALAAgADAALgAyADYAOAA1ACwAIAAwAC4AMAAxADMANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAXAB1ADAAMAAzAGMAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAxADAALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgA3ADIALAAgADAALgA3ADYALAAgADAALgA4ACwAIAAwAC4ANwA4ACwAIAAwAC4ANwA0ACwAIAAwAC4ANgA5ACwAIAAwAC4ANwAzACwAIAAwAC4ANwA2ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAIAAoAGEAKQBcACIALAAgADAALgAxADUALAAgADAALgAxADgALAAgADAALgA1ADAALAAgADAALgAyADQALAAgADAALgAxADcALAAgADAALgAxADMALAAgADAALgAxADcALAAgADAALgAxADgALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBtADsAIABGAHIAYQBjAEcAQQBTAE0AbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkACkAXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQA0ACAAUABhAHMAdAB1AHIAZQBcACIALAAgADAALAAgADAALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgADAALgAwADcALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAUABhAGQAZABvAGMAawBcACIALAAgADAALAAgADAALgAyACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAzACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBQAFcARQBOAFQARQBSAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAwAC4AMAAxADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIABcAHUAMAAwADIANwBBAG4AbgB1AGEAbAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaQBtAGUAIABzAHAAZQBuAHQAIABwAGUAcgAgAGEAcgBlAGEAXAB1ADAAMAAyADcAIAByAG8AdwAgAGEAcwAgAHQAaABpAHMAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AIABpAHMAIABpAG4AIAB0AGgAZQAgAHQAYQBiAGwAZQAgAHQAaQB0AGwAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcgBlAGEAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAUwBoAGUAZABcACIALAAgAFwAIgBGAGUAZQBkAHAAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADEAOgAgAEcAcgBhAHoAZQBkACAATwBuAGwAeQBcACIALAAgADAALgA4ADkALAAgADAALgAxADEALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAyADoAIABPAG4AIABmAGUAZQBkAHAAYQBkACAAZgBvAHIAIABcAHUAMAAwADMAYwAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAXAB1ADAAMAAzAGMAMwAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA3ADkALAAgADAALgAxADEALAAgADAALgAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAzADoAIABQAGEAcwB0AHUAcgBlAC0AZwByAGEAegBlAGQAIAAzAC0AOQAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA1ADMANAAsACAAMAAuADEAMQAsACAAMAAuADMANQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAANAA6ACAAWgBlAHIAbwAgAGcAcgBhAHoAaQBuAGcAXAAiACwAIAAwACwAIAAwAC4AMQAxACwAIAAwAC4AOAA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQAgAHkAZQBhAHIAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAFwAbgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAUABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQATQBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA3ADUAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBcAG4ATgBlAHQAIABlAG4AZQByAGcAeQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAvACAAawBnACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAwADUANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AFwAbgBHAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAZAByAHkAIABtAGEAdAB0AGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcARQBDAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEoAIAAvACAAawBnAEQATQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADEAOAAuADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBcAG4ARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIAB1AHMAZQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAOAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAXwBvAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMQAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARABlAGYAYQB1AGwAdAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAdwBoAGUAbgAgAG0AYQBuAHUAcgBlACAAaQBzACAAZQB4AGMAcgBlAHQAZQBkACAAdABvACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAKABtAD0AMQA0ACkALgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAegBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXABuAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgAgAEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0AC4AMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4AUAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAEMAXwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAzAC4AMwApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADMAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABEAGEAaQByAHkAIABDAGEAdAB0AGwAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9ACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAMQAyADQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADEAMgA0ACAAPQAgAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADEAMgA0ACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABkAGEAeQBzACkAXABuAE4AXwBqADMANQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAaABlAGEAZAApAFwAbgBNAF8AagAzADUAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBEAF8AagAzADUAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAZABhAHkAcwApAFwAbgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAxADIANAAsACAATQBfAGoAMQAyADQALAAgAEQAXwBqADEAMgA0ACwAIABOAF8AagAzADUALAAgAE0AXwBqADMANQAsACAARABfAGoAMwA1ACwAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAsAFwAbgAgACAAIAAgACgAKABOAF8AagAxADIANAAgACoAIABNAF8AagAxADIANAAgACoAIABEAF8AagAxADIANAApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AXwBqADMANQAgACoAIABEAF8AagAzADUAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgACoAIABEAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAEQAUABXAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAUABXAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABQAFcAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAxADIANABcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAzADUAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABQAFcAXwBqADMANQBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEQAUABXAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -24771,31 +24926,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQwBvAHcAcwAgAGEAbgBkACAASABlAGkAZgBlAHIAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAJwBSAGUAZgBlAHIAZQBuAGMAZQAnACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAJwBEAGEAaQByAHkAIABBAHUAcwB0AHIAYQBsAGkAYQAgAFsAMQBdACcAIABhAG4AZAAgAGkAcwAgAG4AbwB0ACAAdQBzAGUAZAAgAGkAbgAgAGMAYQBsAGMAdQBsAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBkAGkAdQBtACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANQA1ADAALAAgADMAOAAwACwAIAAxADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAcgBnAGUAIABGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADAAMAAsACAANAAxADUALAAgADEANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBsAHMAdABlAGkAbgAtAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADYANQAwACwAIAA0ADUAMAAsACAAMQA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGkAZQBzAGkAYQBuACAAYwByAG8AcwBzAGIAcgBlAGQAXAAiACwAIAA1ADAAMAAsACAAMwA1ADAALAAgADEANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAZQByAHMAZQB5AFwAIgAsACAANAAwADAALAAgADIANwA1ACwAIAAxADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANAA1ADAALAAgADMAMQA1ACwAIAAxADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHkAcgBzAGgAaQByAGUAXAAiACwAIAA1ADQAMAAsACAAMwA3ADUALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAdQBlAHIAbgBzAGUAeQBcACIALAAgADQAOAAwACwAIAAzADMANQAsACAAMQA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAG8AdwBuACAAUwB3AGkAcwBzAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGwAbABhAHcAYQByAHIAYQAvAEEAdQBzAHMAaQBlACAAUgBlAGQAXAAiACwAIAA1ADUAMAAsACAAMwA3ADUALAAgADEANQAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABCAHUAbABsAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAwAC4AMAAxADYALAAgADAALgA2ACwAIAAwAC4ANQA3ACwAIAAwAC4AMQAsACAAMAAuADgAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPgAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAPgAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgADwAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAA1ADkAMAAsACAANQA5ADAALAAgADUAOQAwACwAIAA3ADcAMAAsACAANwA3ADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAPQAzACwANQA7ACAATgBQAFcAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAAnAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagAnACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEMASAA0ACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAPQAzACwANQApAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAEUAeABjAHIAZQB0AGUAZAAgACgATgBQAFcAagA9ADMALAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzADwAMQBcACIALAAgADAALgAwADEANwA2ACwAIAAwAC4AMgA2ADgANQAsACAAMAAuADAAMQAzADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzADwAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMQAwACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwAC4ANwAyACwAIAAwAC4ANwA2ACwAIAAwAC4AOAAsACAAMAAuADcAOAAsACAAMAAuADcANAAsACAAMAAuADYAOQAsACAAMAAuADcAMwAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AcwBcACIALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzACAAKABhACkAXAAiACwAIAAwAC4AMQA1ACwAIAAwAC4AMQA4ACwAIAAwAC4ANQAwACwAIAAwAC4AMgA0ACwAIAAwAC4AMQA3ACwAIAAwAC4AMQAzACwAIAAwAC4AMQA3ACwAIAAwAC4AMQA4ACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQA7ACAARgByAGEAYwBHAEEAUwBNAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlACcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZAApAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAEQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAMAAuADAANwAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABQAGEAZABkAG8AYwBrAFwAIgAsACAAMAAsACAAMAAuADIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAMAAuADMALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMQA3ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIAAnAEEAbgBuAHUAYQBsACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABpAG0AZQAgAHMAcABlAG4AdAAgAHAAZQByACAAYQByAGUAYQAnACAAcgBvAHcAIABhAHMAIAB0AGgAaQBzACAAaQBuAGYAbwByAG0AYQB0AGkAbwBuACAAaQBzACAAaQBuACAAdABoAGUAIAB0AGEAYgBsAGUAIAB0AGkAdABsAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHIAZQBhAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAFMAaABlAGQAXAAiACwAIABcACIARgBlAGUAZABwAGEAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAxADoAIABHAHIAYQB6AGUAZAAgAE8AbgBsAHkAXAAiACwAIAAwAC4AOAA5ACwAIAAwAC4AMQAxACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMgA6ACAATwBuACAAZgBlAGUAZABwAGEAZAAgAGYAbwByACAAPAAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAPAAzACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADcAOQAsACAAMAAuADEAMQAsACAAMAAuADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADMAOgAgAFAAYQBzAHQAdQByAGUALQBnAHIAYQB6AGUAZAAgADMALQA5ACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADUAMwA0ACwAIAAwAC4AMQAxACwAIAAwAC4AMwA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAA0ADoAIABaAGUAcgBvACAAZwByAGEAegBpAG4AZwBcACIALAAgADAALAAgADAALgAxADEALAAgADAALgA4ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIAA8ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAD4AIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgADwAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXABuAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBQAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcAG4ARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABNAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADcANQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AFwAbgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AZQB0ACAAZQBuAGUAcgBnAHkAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAgAC8AIABrAGcAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMwAuADAANQA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXABuAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBFAEMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcARABNAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQA4AC4ANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AFwAbgBFAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAdQBzAGUAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAA4ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBfAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAxADEAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAXwBMAEUAQQBDAEgAXwBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHoAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4ARgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBDAF8AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQALgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAFwAbgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADIAIABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAzACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARABhAGkAcgB5ACAAQwBhAHQAdABsAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAzAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAxADIANAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAMQAyADQAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANAAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAMQAyADQAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGQAYQB5AHMAKQBcAG4ATgBfAGoAMwA1ACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADMANQAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABkAGEAeQBzACkAXABuAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoAMQAyADQALAAgAE0AXwBqADEAMgA0ACwAIABEAF8AagAxADIANAAsACAATgBfAGoAMwA1ACwAIABNAF8AagAzADUALAAgAEQAXwBqADMANQAsACAARABQAFcAXwBqADMANQAsACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUALABcAG4AIAAgACAAIAAoACgATgBfAGoAMQAyADQAIAAqACAATQBfAGoAMQAyADQAIAAqACAARABfAGoAMQAyADQAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAF8AagAzADUAIAAqACAARABfAGoAMwA1ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAIAAqACAARABQAFcAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAFAAVwBfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADEAMgA0AFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMQAyADQAXAAiACwAIABcACIAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMQAyADQAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADMANQBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMwA1AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagAzADUAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAFAAVwBfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBEAFAAVwAnACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24812,31 +24970,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82590345-C4B9-4651-B808-B580B2BAE45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E6DA0-202E-44AB-BCF9-FFA4154B82B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -24,9 +24,6 @@
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId11"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -298,6 +295,30 @@
     <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
     <definedName name="InputFunctions_Dairy.CalculateFractionInMMSAfterSolidSeparation">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.MMSFraction,_xlpm.FractionSeparated, _xlpm.ProductionSystem * (_xlpm.MMSFraction - (_xlpm.MMSFraction * _xlpm.FractionSeparated)))</definedName>
     <definedName name="InputFunctions_Dairy.CalculateFractionInSolidStorage">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.InitalSolidStorageFraction,_xlpm.MMS1Fraction,_xlpm.MMS1Separated,_xlpm.MMS2Fraction,_xlpm.MMS2Separated,_xlpm.MMS3Fraction,_xlpm.MMS3Separated, _xlpm.ProductionSystem * (_xlpm.InitalSolidStorageFraction + (_xlpm.MMS1Fraction * _xlpm.MMS1Separated) + (_xlpm.MMS2Fraction * _xlpm.MMS2Separated) + (_xlpm.MMS3Fraction * _xlpm.MMS3Separated)))</definedName>
+    <definedName name="M1_Table_D_j">'3.3.1.1-2 Enteric Methane'!$D$164:$H$165</definedName>
+    <definedName name="M1_Table_DMD_j">'3.3.1.1-2 Enteric Methane'!$D$18:$H$19</definedName>
+    <definedName name="M1_Table_DPW_j35">'3.3.1.1-2 Enteric Methane'!$D$169:$H$170</definedName>
+    <definedName name="M1_Table_E_enteric">'3.3.1.1-2 Enteric Methane'!$M$179:$Q$180</definedName>
+    <definedName name="M1_Table_E_enteric_Consumer_1">'3.3.1.1-2 Enteric Methane'!$D$179:$H$180</definedName>
+    <definedName name="M1_Table_I_j">'3.3.1.1-2 Enteric Methane'!$D$114:$H$115</definedName>
+    <definedName name="M1_Table_LWG_j">'3.3.1.1-2 Enteric Methane'!$D$104:$H$105</definedName>
+    <definedName name="M1_Table_M_j">'3.3.1.1-2 Enteric Methane'!$D$131:$H$132</definedName>
+    <definedName name="M1_Table_MI_j">'3.3.1.1-2 Enteric Methane'!$D$79:$H$80</definedName>
+    <definedName name="M1_Table_MP_j_from_solids">'3.3.1.1-2 Enteric Methane'!$D$49:$H$50</definedName>
+    <definedName name="M1_Table_MPW_j35">'3.3.1.1-2 Enteric Methane'!$D$174:$E$175</definedName>
+    <definedName name="M1_Table_MS_j">'3.3.1.1-2 Enteric Methane'!$D$44:$H$45</definedName>
+    <definedName name="M1_Table_qm_j">'3.3.1.1-2 Enteric Methane'!$D$23:$H$24</definedName>
+    <definedName name="M1_Table_W_j">'3.3.1.1-2 Enteric Methane'!$D$99:$H$100</definedName>
+    <definedName name="M2_Table_D_j">'3.3.1.1-2 Enteric Methane'!$M$164:$Q$165</definedName>
+    <definedName name="M2_Table_DMD_j">'3.3.1.1-2 Enteric Methane'!$M$18:$Q$19</definedName>
+    <definedName name="M2_Table_DPW_j">'3.3.1.1-2 Enteric Methane'!$M$169:$Q$170</definedName>
+    <definedName name="M2_Table_I_j">'3.3.1.1-2 Enteric Methane'!$M$114:$Q$115</definedName>
+    <definedName name="M2_Table_LWG_j">'3.3.1.1-2 Enteric Methane'!$M$104:$Q$105</definedName>
+    <definedName name="M2_Table_M_j">'3.3.1.1-2 Enteric Methane'!$M$131:$Q$132</definedName>
+    <definedName name="M2_Table_MI_j">'3.3.1.1-2 Enteric Methane'!$M$79:$Q$80</definedName>
+    <definedName name="M2_Table_MP_j_from_solids">'3.3.1.1-2 Enteric Methane'!$M$49:$Q$50</definedName>
+    <definedName name="M2_Table_qm_j">'3.3.1.1-2 Enteric Methane'!$M$23:$Q$24</definedName>
+    <definedName name="M2_Table_W_j">'3.3.1.1-2 Enteric Methane'!$M$99:$Q$100</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_AshContent_Data">_xlfn.LAMBDA(0.08)</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_AshContent_Source">_xlfn.LAMBDA("VEERG 2026: 4.3.2.3 CONSTANTS")</definedName>
@@ -446,6 +467,9 @@
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
+    <definedName name="Table_MP_j">'3.3.1.1-2 Enteric Methane'!$D$74:$H$75</definedName>
+    <definedName name="Table_MR_j">'3.3.1.1-2 Enteric Methane'!$D$109:$H$110</definedName>
+    <definedName name="Table_N_j">'3.3.1.1-2 Enteric Methane'!$D$159:$H$160</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2780,6 +2804,746 @@
   <dxfs count="94">
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB2D498"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3641,746 +4405,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB2D498"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9051,26 +9075,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -9143,7 +9147,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="81" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="45" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9161,13 +9165,13 @@
     <tableColumn id="1" xr3:uid="{8ACEF380-8A1A-411E-A23A-665A769E20C7}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9185,7 +9189,7 @@
     <tableColumn id="1" xr3:uid="{34872B36-E9B0-443E-A8EC-EC35C2572085}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9203,7 +9207,7 @@
     <tableColumn id="1" xr3:uid="{B2383F7B-29D1-4559-9E34-4E2C127CFB5C}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9223,13 +9227,13 @@
     <tableColumn id="1" xr3:uid="{A4A196FD-DBDB-46C0-83CE-7C77F2C477B3}" name="Area">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9248,10 +9252,10 @@
     <tableColumn id="1" xr3:uid="{D85FDEBC-2FC0-45F1-BCD6-4464E2C22E94}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9270,10 +9274,10 @@
     <tableColumn id="1" xr3:uid="{C1D0CE9E-4549-48D9-9C0F-1310FC73ABC5}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9403,49 +9407,49 @@
     <tableColumn id="1" xr3:uid="{D27ECB6B-999A-4BD3-B047-A5AAC859AEAF}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AA6488F9-231D-4939-BDFA-B7CBED91888F}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{AA6488F9-231D-4939-BDFA-B7CBED91888F}" name="MAT" totalsRowDxfId="81" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{ADC6FD29-BC7C-4785-98DB-9C4A3BCEB1D0}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{ADC6FD29-BC7C-4785-98DB-9C4A3BCEB1D0}" name="MAP" totalsRowDxfId="80" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{466645EB-B94B-4DF4-8EA0-096EA00E81FB}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{466645EB-B94B-4DF4-8EA0-096EA00E81FB}" name="Frost days per year" totalsRowDxfId="79" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BE315AAD-BE19-47C8-AB5F-4B616B19F040}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{BE315AAD-BE19-47C8-AB5F-4B616B19F040}" name="Elevation" totalsRowDxfId="78" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DF314910-84DB-47B1-B381-B405E58B2391}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DF314910-84DB-47B1-B381-B405E58B2391}" name="MAP:PET" totalsRowDxfId="77" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2FDF8B6B-762F-4F7C-BAD1-E14E0BEE7BB6}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{2FDF8B6B-762F-4F7C-BAD1-E14E0BEE7BB6}" name="Min temp" totalsRowDxfId="76" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{07863784-E03B-4255-B45B-3F0FDC32B807}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{07863784-E03B-4255-B45B-3F0FDC32B807}" name="Max temp" totalsRowDxfId="75" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A3A2332-0D79-4AF0-BFF9-195AC9D36A9B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{8A3A2332-0D79-4AF0-BFF9-195AC9D36A9B}" name="Min rainfall" totalsRowDxfId="74" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E8A1FA8-7602-40D4-9D62-C0743544DC8C}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1E8A1FA8-7602-40D4-9D62-C0743544DC8C}" name="Max rainfall" totalsRowDxfId="73" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{474010DE-FFE2-4FBE-837A-9ABC26E1FFA6}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{474010DE-FFE2-4FBE-837A-9ABC26E1FFA6}" name="Min frost days" totalsRowDxfId="72" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{6222BDCD-C79D-473D-B3B9-61585F481A20}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{6222BDCD-C79D-473D-B3B9-61585F481A20}" name="Max frost days" totalsRowDxfId="71" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E30A3D94-830C-4D5F-9910-B32467D45A59}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{E30A3D94-830C-4D5F-9910-B32467D45A59}" name="Min elevation" totalsRowDxfId="70" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C9BEB83-BFDD-4486-A2AF-1A8246AE2001}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{1C9BEB83-BFDD-4486-A2AF-1A8246AE2001}" name="Max elevation" totalsRowDxfId="69" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E9C2232B-89B7-4599-807F-84A1995BE780}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E9C2232B-89B7-4599-807F-84A1995BE780}" name="Min MAP:PET" totalsRowDxfId="68" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{B65144AE-98E9-4B77-A979-5D7E8FD05C90}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{B65144AE-98E9-4B77-A979-5D7E8FD05C90}" name="Max MAP:PET" totalsRowDxfId="67" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9463,7 +9467,7 @@
     <tableColumn id="1" xr3:uid="{C264AE15-9D43-4230-8CF3-005ACA80737C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6A705B5-3BB9-4F52-AE9B-8647BEFF7A17}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F6A705B5-3BB9-4F52-AE9B-8647BEFF7A17}" name="Wet or Dry Zone" totalsRowDxfId="66" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9569,7 +9573,7 @@
     <tableColumn id="1" xr3:uid="{627D4BA3-08BB-4BFD-80C4-18A175949150}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{21DB7D11-31D2-41AB-A91C-AB83B43E2E99}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{21DB7D11-31D2-41AB-A91C-AB83B43E2E99}" name="FracWET" dataDxfId="65">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9617,7 +9621,7 @@
     <tableColumn id="1" xr3:uid="{1CEC1953-8E56-4FD4-BC26-3865CAACC286}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F42D44F-1CF8-49F4-81D0-03F6A55595DF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3F42D44F-1CF8-49F4-81D0-03F6A55595DF}" name="FracWET" dataDxfId="64" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9635,7 +9639,7 @@
     <tableColumn id="1" xr3:uid="{E3913DC5-18BF-4429-B563-93C6A8F41687}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{84A849F0-4488-4D62-AD7E-B9EC4921BE0E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{84A849F0-4488-4D62-AD7E-B9EC4921BE0E}" name="EFPRP" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9665,7 +9669,7 @@
     <tableColumn id="1" xr3:uid="{5BE0D823-5222-434D-9E2E-2F0E4EFE4D24}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CAFE497D-DA77-442E-8064-29E27FA514E4}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CAFE497D-DA77-442E-8064-29E27FA514E4}" name="Season" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9697,49 +9701,49 @@
     <tableColumn id="1" xr3:uid="{B44084F6-B587-4CAE-8739-AC4B37EFE76F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BDA08BD-756F-4B06-BAEC-1C98826106F0}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4BDA08BD-756F-4B06-BAEC-1C98826106F0}" name="MAT (ºC)" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A7303D30-0C89-45D2-B4E1-EA0EF1649503}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A7303D30-0C89-45D2-B4E1-EA0EF1649503}" name="Anaerobic lagoon" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C6E7430C-F8AE-4940-BB83-93D2E45DAF4D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{C6E7430C-F8AE-4940-BB83-93D2E45DAF4D}" name="Digester / covered lagoons" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FF1C7AF5-F58D-4463-857A-E226C8720E94}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FF1C7AF5-F58D-4463-857A-E226C8720E94}" name="Liquid systems" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4B0ACC6E-B49C-4D66-8D15-452C3D392828}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4B0ACC6E-B49C-4D66-8D15-452C3D392828}" name="Daily spread" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{73EDE90B-A287-40DA-BAB9-8974CE978C2F}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{73EDE90B-A287-40DA-BAB9-8974CE978C2F}" name="Composting (passive windrow)" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{EE40E181-A636-450F-B6D8-50AAA25151B7}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{EE40E181-A636-450F-B6D8-50AAA25151B7}" name="Solid storage" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C3264EAA-7EED-4B15-84F6-E857933D554C}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{C3264EAA-7EED-4B15-84F6-E857933D554C}" name="Pit storage" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ED6C1257-139D-4E34-B207-7A36AA4BD374}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{ED6C1257-139D-4E34-B207-7A36AA4BD374}" name="Deep litter" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF40561E-7552-45AE-BD73-BD4FE67EFCBE}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{FF40561E-7552-45AE-BD73-BD4FE67EFCBE}" name="Poultry manure with bedding" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6F8E8A90-DFE4-49D8-937A-D94686DE505C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6F8E8A90-DFE4-49D8-937A-D94686DE505C}" name="Poultry manure without bedding" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{755860C4-2725-4DA6-8D53-0AF45AFD38DB}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{755860C4-2725-4DA6-8D53-0AF45AFD38DB}" name="Direct processing" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{0431DBA3-DB30-4D87-BEA7-2ACCE4C7A076}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{0431DBA3-DB30-4D87-BEA7-2ACCE4C7A076}" name="Direct application" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{FD82C3C0-5829-41E9-9B97-A0692E3C9093}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{FD82C3C0-5829-41E9-9B97-A0692E3C9093}" name="Pasture range and paddock" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C0CF46EB-58DB-48D5-9751-7E6B0D642CAB}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C0CF46EB-58DB-48D5-9751-7E6B0D642CAB}" name="MAT raw" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9757,7 +9761,7 @@
     <tableColumn id="1" xr3:uid="{6DFBEF8F-8540-41EE-B08C-9E7C56290E48}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF94C142-CC61-437C-87D9-52B720B134A8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AF94C142-CC61-437C-87D9-52B720B134A8}" name="EFNi &amp; EFN2Oi" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9799,13 +9803,13 @@
     <tableColumn id="1" xr3:uid="{CAC4C566-E7DF-44B3-BDB4-4B1785D5F9F0}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="80" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="79" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="78" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="42" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9824,10 +9828,10 @@
     <tableColumn id="1" xr3:uid="{40374F5E-9BC3-4080-A28F-8B1F65DE1774}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="77" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="41" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="76" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="40" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9848,16 +9852,16 @@
     <tableColumn id="1" xr3:uid="{69C0AC05-6C13-494A-8124-C36C4B6D01B6}" name="Milking cows">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="75" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="74" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="38" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="73" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="37" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="72" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9866,7 +9870,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="71" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D54:H55" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9896,7 +9900,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="70" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="34" dataCellStyle="Content normal">
   <autoFilter ref="D62:G64" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9904,16 +9908,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="69" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="68" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="67" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="66" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9939,31 +9943,31 @@
     <tableColumn id="1" xr3:uid="{A54F6170-CD83-454D-874A-2A78490F2BD1}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="65" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="64" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="63" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="60" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15121,47 +15125,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E10:M10 E24:M25 E28:M29 O43:P43 N44 J85:J90 K89:M89 K95:M95 F98 J101:J106 K105:M105 K110:M110 K114:M114 K123:M123">
-    <cfRule type="cellIs" dxfId="44" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="30" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:M15">
-    <cfRule type="cellIs" dxfId="43" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:M19">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36:M38">
-    <cfRule type="cellIs" dxfId="41" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:M43">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87:F88">
-    <cfRule type="cellIs" dxfId="39" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91">
-    <cfRule type="cellIs" dxfId="38" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K65:M67">
-    <cfRule type="cellIs" dxfId="37" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="24" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K70:M72">
-    <cfRule type="cellIs" dxfId="36" priority="23" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="23" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24712,26 +24716,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -24926,6 +24910,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
@@ -24935,25 +24939,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24970,4 +24955,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8E6DA0-202E-44AB-BCF9-FFA4154B82B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9374AE3A-8F48-4E24-958F-C4F43063A3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -470,6 +470,39 @@
     <definedName name="Table_MP_j">'3.3.1.1-2 Enteric Methane'!$D$74:$H$75</definedName>
     <definedName name="Table_MR_j">'3.3.1.1-2 Enteric Methane'!$D$109:$H$110</definedName>
     <definedName name="Table_N_j">'3.3.1.1-2 Enteric Methane'!$D$159:$H$160</definedName>
+    <definedName name="VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentationVariation_Result_Method1">'3.3.1.1-2 Enteric Methane'!$E$182</definedName>
+    <definedName name="VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentationVariation_Result_Method2">'3.3.1.1-2 Enteric Methane'!$N$182</definedName>
+    <definedName name="X_Cell_Dairy_Breed">'Input - Dairy'!$E$7</definedName>
+    <definedName name="X_Cell_Dairy_MilkProductionAmount">'Input - Dairy'!$E$52</definedName>
+    <definedName name="X_Cell_Dairy_MilkProductionUnit">'Input - Dairy'!$E$49</definedName>
+    <definedName name="X_Cell_Dairy_MilkSolidsFatContent_Method1">'Input - Dairy'!$E$55</definedName>
+    <definedName name="X_Cell_Dairy_MilkSolidsFatContent_Method2">'Input - Dairy'!$F$55</definedName>
+    <definedName name="X_Cell_Dairy_MilkSolidsProteinContent_Method1">'Input - Dairy'!$F$56</definedName>
+    <definedName name="X_Cell_Dairy_MilkSolidsProteinContent_Method2">'Input - Dairy'!$F$56</definedName>
+    <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$25</definedName>
+    <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$31</definedName>
+    <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$24</definedName>
+    <definedName name="X_Cell_Site_EndDate">'Input - Site'!$E$13</definedName>
+    <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
+    <definedName name="X_Cell_Site_FrostDays">'Input - Site'!$E$28</definedName>
+    <definedName name="X_Cell_Site_LeachingZone">'Input - Site'!$E$23</definedName>
+    <definedName name="X_Cell_Site_MapPetRatio">'Input - Site'!$E$29</definedName>
+    <definedName name="X_Cell_Site_PotentialEvapotranspiration">'Input - Site'!$E$27</definedName>
+    <definedName name="X_Cell_Site_RainfallZone">'Input - Site'!$E$30</definedName>
+    <definedName name="X_Cell_Site_Region">'Input - Site'!$E$22</definedName>
+    <definedName name="X_Cell_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
+    <definedName name="X_Cell_Site_StartDate">'Input - Site'!$E$12</definedName>
+    <definedName name="X_Cell_Site_State">'Input - Site'!$E$21</definedName>
+    <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$33</definedName>
+    <definedName name="X_Cell_Site_TotalRainfall">'Input - Site'!$E$26</definedName>
+    <definedName name="X_Cell_Site_WetOrDryClimateZone">'Input - Site'!$E$32</definedName>
+    <definedName name="X_Table_Dairy_Diet_Method1">'Input - Dairy'!$D$35:$I$37</definedName>
+    <definedName name="X_Table_Dairy_Diet_Method2">'Input - Dairy'!$D$39:$I$41</definedName>
+    <definedName name="X_Table_Dairy_DurationOfStay_Method1">'Input - Dairy'!$D$23:$I$25</definedName>
+    <definedName name="X_Table_Dairy_DurationOfStay_Method2">'Input - Dairy'!$D$27:$I$29</definedName>
+    <definedName name="X_Table_Dairy_HerdMovement">'Input - Dairy'!$D$9:$I$10</definedName>
+    <definedName name="X_Table_Dairy_Liveweight_Method1">'Input - Dairy'!$D$13:$I$15</definedName>
+    <definedName name="X_Table_Dairy_Liveweight_Method2">'Input - Dairy'!$D$17:$I$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -529,7 +562,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="253">
   <si>
     <t>Home</t>
   </si>
@@ -1074,13 +1107,7 @@
     <t>Method 1 default values (Do not edit)</t>
   </si>
   <si>
-    <t>Dry matter intake</t>
-  </si>
-  <si>
     <t>Diet</t>
-  </si>
-  <si>
-    <t>kgDM/head/day</t>
   </si>
   <si>
     <t>Liveweight</t>
@@ -2801,7 +2828,7 @@
     <cellStyle name="Variable type input" xfId="67" xr:uid="{8B650911-9251-4CA7-8D5F-FC6CA32FF621}"/>
     <cellStyle name="Variable type other" xfId="65" xr:uid="{B3E8C5CF-C085-4800-95E7-0E14E266DEDE}"/>
   </cellStyles>
-  <dxfs count="94">
+  <dxfs count="92">
     <dxf>
       <font>
         <color rgb="FFC44340"/>
@@ -2871,676 +2898,6 @@
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB2D498"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4648,6 +4005,656 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB2D498"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1" tint="0.24994659260841701"/>
       </font>
       <fill>
@@ -4848,20 +4855,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="93"/>
-      <tableStyleElement type="headerRow" dxfId="92"/>
-      <tableStyleElement type="totalRow" dxfId="91"/>
-      <tableStyleElement type="firstColumn" dxfId="90"/>
-      <tableStyleElement type="firstRowStripe" dxfId="89"/>
-      <tableStyleElement type="secondRowStripe" dxfId="88"/>
+      <tableStyleElement type="wholeTable" dxfId="91"/>
+      <tableStyleElement type="headerRow" dxfId="90"/>
+      <tableStyleElement type="totalRow" dxfId="89"/>
+      <tableStyleElement type="firstColumn" dxfId="88"/>
+      <tableStyleElement type="firstRowStripe" dxfId="87"/>
+      <tableStyleElement type="secondRowStripe" dxfId="86"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="87"/>
-      <tableStyleElement type="headerRow" dxfId="86"/>
-      <tableStyleElement type="totalRow" dxfId="85"/>
-      <tableStyleElement type="firstColumn" dxfId="84"/>
-      <tableStyleElement type="firstRowStripe" dxfId="83"/>
-      <tableStyleElement type="secondRowStripe" dxfId="82"/>
+      <tableStyleElement type="wholeTable" dxfId="85"/>
+      <tableStyleElement type="headerRow" dxfId="84"/>
+      <tableStyleElement type="totalRow" dxfId="83"/>
+      <tableStyleElement type="firstColumn" dxfId="82"/>
+      <tableStyleElement type="firstRowStripe" dxfId="81"/>
+      <tableStyleElement type="secondRowStripe" dxfId="80"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -9147,7 +9154,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="45" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="79" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9165,13 +9172,13 @@
     <tableColumn id="1" xr3:uid="{8ACEF380-8A1A-411E-A23A-665A769E20C7}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9189,7 +9196,7 @@
     <tableColumn id="1" xr3:uid="{34872B36-E9B0-443E-A8EC-EC35C2572085}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9207,7 +9214,7 @@
     <tableColumn id="1" xr3:uid="{B2383F7B-29D1-4559-9E34-4E2C127CFB5C}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9227,13 +9234,13 @@
     <tableColumn id="1" xr3:uid="{A4A196FD-DBDB-46C0-83CE-7C77F2C477B3}" name="Area">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9252,10 +9259,10 @@
     <tableColumn id="1" xr3:uid="{D85FDEBC-2FC0-45F1-BCD6-4464E2C22E94}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9274,10 +9281,10 @@
     <tableColumn id="1" xr3:uid="{C1D0CE9E-4549-48D9-9C0F-1310FC73ABC5}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="43" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9407,49 +9414,49 @@
     <tableColumn id="1" xr3:uid="{D27ECB6B-999A-4BD3-B047-A5AAC859AEAF}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AA6488F9-231D-4939-BDFA-B7CBED91888F}" name="MAT" totalsRowDxfId="81" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{AA6488F9-231D-4939-BDFA-B7CBED91888F}" name="MAT" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{ADC6FD29-BC7C-4785-98DB-9C4A3BCEB1D0}" name="MAP" totalsRowDxfId="80" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{ADC6FD29-BC7C-4785-98DB-9C4A3BCEB1D0}" name="MAP" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{466645EB-B94B-4DF4-8EA0-096EA00E81FB}" name="Frost days per year" totalsRowDxfId="79" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{466645EB-B94B-4DF4-8EA0-096EA00E81FB}" name="Frost days per year" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BE315AAD-BE19-47C8-AB5F-4B616B19F040}" name="Elevation" totalsRowDxfId="78" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{BE315AAD-BE19-47C8-AB5F-4B616B19F040}" name="Elevation" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DF314910-84DB-47B1-B381-B405E58B2391}" name="MAP:PET" totalsRowDxfId="77" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{DF314910-84DB-47B1-B381-B405E58B2391}" name="MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2FDF8B6B-762F-4F7C-BAD1-E14E0BEE7BB6}" name="Min temp" totalsRowDxfId="76" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{2FDF8B6B-762F-4F7C-BAD1-E14E0BEE7BB6}" name="Min temp" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{07863784-E03B-4255-B45B-3F0FDC32B807}" name="Max temp" totalsRowDxfId="75" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{07863784-E03B-4255-B45B-3F0FDC32B807}" name="Max temp" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A3A2332-0D79-4AF0-BFF9-195AC9D36A9B}" name="Min rainfall" totalsRowDxfId="74" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{8A3A2332-0D79-4AF0-BFF9-195AC9D36A9B}" name="Min rainfall" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E8A1FA8-7602-40D4-9D62-C0743544DC8C}" name="Max rainfall" totalsRowDxfId="73" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1E8A1FA8-7602-40D4-9D62-C0743544DC8C}" name="Max rainfall" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{474010DE-FFE2-4FBE-837A-9ABC26E1FFA6}" name="Min frost days" totalsRowDxfId="72" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{474010DE-FFE2-4FBE-837A-9ABC26E1FFA6}" name="Min frost days" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{6222BDCD-C79D-473D-B3B9-61585F481A20}" name="Max frost days" totalsRowDxfId="71" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{6222BDCD-C79D-473D-B3B9-61585F481A20}" name="Max frost days" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E30A3D94-830C-4D5F-9910-B32467D45A59}" name="Min elevation" totalsRowDxfId="70" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{E30A3D94-830C-4D5F-9910-B32467D45A59}" name="Min elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C9BEB83-BFDD-4486-A2AF-1A8246AE2001}" name="Max elevation" totalsRowDxfId="69" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{1C9BEB83-BFDD-4486-A2AF-1A8246AE2001}" name="Max elevation" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E9C2232B-89B7-4599-807F-84A1995BE780}" name="Min MAP:PET" totalsRowDxfId="68" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{E9C2232B-89B7-4599-807F-84A1995BE780}" name="Min MAP:PET" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{B65144AE-98E9-4B77-A979-5D7E8FD05C90}" name="Max MAP:PET" totalsRowDxfId="67" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{B65144AE-98E9-4B77-A979-5D7E8FD05C90}" name="Max MAP:PET" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9467,7 +9474,7 @@
     <tableColumn id="1" xr3:uid="{C264AE15-9D43-4230-8CF3-005ACA80737C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6A705B5-3BB9-4F52-AE9B-8647BEFF7A17}" name="Wet or Dry Zone" totalsRowDxfId="66" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F6A705B5-3BB9-4F52-AE9B-8647BEFF7A17}" name="Wet or Dry Zone" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9573,7 +9580,7 @@
     <tableColumn id="1" xr3:uid="{627D4BA3-08BB-4BFD-80C4-18A175949150}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{21DB7D11-31D2-41AB-A91C-AB83B43E2E99}" name="FracWET" dataDxfId="65">
+    <tableColumn id="2" xr3:uid="{21DB7D11-31D2-41AB-A91C-AB83B43E2E99}" name="FracWET" dataDxfId="26">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9621,7 +9628,7 @@
     <tableColumn id="1" xr3:uid="{1CEC1953-8E56-4FD4-BC26-3865CAACC286}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F42D44F-1CF8-49F4-81D0-03F6A55595DF}" name="FracWET" dataDxfId="64" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3F42D44F-1CF8-49F4-81D0-03F6A55595DF}" name="FracWET" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9639,7 +9646,7 @@
     <tableColumn id="1" xr3:uid="{E3913DC5-18BF-4429-B563-93C6A8F41687}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{84A849F0-4488-4D62-AD7E-B9EC4921BE0E}" name="EFPRP" dataDxfId="63" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{84A849F0-4488-4D62-AD7E-B9EC4921BE0E}" name="EFPRP" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9669,7 +9676,7 @@
     <tableColumn id="1" xr3:uid="{5BE0D823-5222-434D-9E2E-2F0E4EFE4D24}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CAFE497D-DA77-442E-8064-29E27FA514E4}" name="Season" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{CAFE497D-DA77-442E-8064-29E27FA514E4}" name="Season" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9701,49 +9708,49 @@
     <tableColumn id="1" xr3:uid="{B44084F6-B587-4CAE-8739-AC4B37EFE76F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4BDA08BD-756F-4B06-BAEC-1C98826106F0}" name="MAT (ºC)" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4BDA08BD-756F-4B06-BAEC-1C98826106F0}" name="MAT (ºC)" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A7303D30-0C89-45D2-B4E1-EA0EF1649503}" name="Anaerobic lagoon" dataDxfId="60" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A7303D30-0C89-45D2-B4E1-EA0EF1649503}" name="Anaerobic lagoon" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C6E7430C-F8AE-4940-BB83-93D2E45DAF4D}" name="Digester / covered lagoons" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{C6E7430C-F8AE-4940-BB83-93D2E45DAF4D}" name="Digester / covered lagoons" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FF1C7AF5-F58D-4463-857A-E226C8720E94}" name="Liquid systems" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FF1C7AF5-F58D-4463-857A-E226C8720E94}" name="Liquid systems" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4B0ACC6E-B49C-4D66-8D15-452C3D392828}" name="Daily spread" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4B0ACC6E-B49C-4D66-8D15-452C3D392828}" name="Daily spread" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{73EDE90B-A287-40DA-BAB9-8974CE978C2F}" name="Composting (passive windrow)" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{73EDE90B-A287-40DA-BAB9-8974CE978C2F}" name="Composting (passive windrow)" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{EE40E181-A636-450F-B6D8-50AAA25151B7}" name="Solid storage" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{EE40E181-A636-450F-B6D8-50AAA25151B7}" name="Solid storage" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C3264EAA-7EED-4B15-84F6-E857933D554C}" name="Pit storage" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{C3264EAA-7EED-4B15-84F6-E857933D554C}" name="Pit storage" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ED6C1257-139D-4E34-B207-7A36AA4BD374}" name="Deep litter" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{ED6C1257-139D-4E34-B207-7A36AA4BD374}" name="Deep litter" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF40561E-7552-45AE-BD73-BD4FE67EFCBE}" name="Poultry manure with bedding" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{FF40561E-7552-45AE-BD73-BD4FE67EFCBE}" name="Poultry manure with bedding" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6F8E8A90-DFE4-49D8-937A-D94686DE505C}" name="Poultry manure without bedding" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6F8E8A90-DFE4-49D8-937A-D94686DE505C}" name="Poultry manure without bedding" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{755860C4-2725-4DA6-8D53-0AF45AFD38DB}" name="Direct processing" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{755860C4-2725-4DA6-8D53-0AF45AFD38DB}" name="Direct processing" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{0431DBA3-DB30-4D87-BEA7-2ACCE4C7A076}" name="Direct application" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{0431DBA3-DB30-4D87-BEA7-2ACCE4C7A076}" name="Direct application" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{FD82C3C0-5829-41E9-9B97-A0692E3C9093}" name="Pasture range and paddock" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{FD82C3C0-5829-41E9-9B97-A0692E3C9093}" name="Pasture range and paddock" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C0CF46EB-58DB-48D5-9751-7E6B0D642CAB}" name="MAT raw" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C0CF46EB-58DB-48D5-9751-7E6B0D642CAB}" name="MAT raw" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9761,7 +9768,7 @@
     <tableColumn id="1" xr3:uid="{6DFBEF8F-8540-41EE-B08C-9E7C56290E48}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AF94C142-CC61-437C-87D9-52B720B134A8}" name="EFNi &amp; EFN2Oi" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AF94C142-CC61-437C-87D9-52B720B134A8}" name="EFNi &amp; EFN2Oi" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9803,13 +9810,13 @@
     <tableColumn id="1" xr3:uid="{CAC4C566-E7DF-44B3-BDB4-4B1785D5F9F0}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="44" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="43" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9828,10 +9835,10 @@
     <tableColumn id="1" xr3:uid="{40374F5E-9BC3-4080-A28F-8B1F65DE1774}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="74" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9852,16 +9859,16 @@
     <tableColumn id="1" xr3:uid="{69C0AC05-6C13-494A-8124-C36C4B6D01B6}" name="Milking cows">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="73" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="72" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="71" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="70" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9870,7 +9877,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="69" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D54:H55" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9900,7 +9907,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="34" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="68" dataCellStyle="Content normal">
   <autoFilter ref="D62:G64" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9908,16 +9915,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="67" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="66" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="65" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="64" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9943,31 +9950,31 @@
     <tableColumn id="1" xr3:uid="{A54F6170-CD83-454D-874A-2A78490F2BD1}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10250,7 +10257,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -10272,7 +10279,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="126" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D1" s="127"/>
       <c r="E1" s="127"/>
@@ -10390,7 +10397,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="130" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E5" s="130"/>
       <c r="F5" s="130"/>
@@ -10416,7 +10423,7 @@
       <c r="A6" s="16"/>
       <c r="C6" s="1"/>
       <c r="D6" s="131" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E6" s="129"/>
       <c r="F6" s="129"/>
@@ -12045,7 +12052,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="115" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12106,19 +12113,19 @@
         <v>109</v>
       </c>
       <c r="E6" s="113" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F6" s="113" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G6" s="113" t="s">
         <v>123</v>
       </c>
       <c r="H6" s="113" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I6" s="113" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J6" s="113" t="s">
         <v>124</v>
@@ -12131,7 +12138,7 @@
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E7" s="111">
         <f>'3.3.1.1-2 Enteric Methane'!E182</f>
@@ -12154,7 +12161,7 @@
         <v>909.01111515171999</v>
       </c>
       <c r="J7" s="56" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K7" s="24"/>
     </row>
@@ -12179,7 +12186,7 @@
         <v>909.01111515171999</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K8" s="24"/>
     </row>
@@ -13992,7 +13999,7 @@
         <v>127</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>9</v>
@@ -14072,7 +14079,7 @@
         <v>3.3.1.1-2 Enteric Methane</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="R12" s="7"/>
     </row>
@@ -14103,7 +14110,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E14" s="54" cm="1">
         <f t="array" ref="E14">Common_InputFunctions.Utility_LookupValueInTableNumber($E$7, Table_SourceData_Dairy_WjCowsHeifers[Breed],Table_SourceData_Dairy_WjCowsHeifers[Milking cows])</f>
@@ -14139,7 +14146,7 @@
         <v>Constants - Dairy</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E15" s="54" cm="1">
         <f t="array" ref="E15">Table_SourceData_Dairy_LWGj[Milking cows]</f>
@@ -14207,7 +14214,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E18" s="67" cm="1">
         <f t="array" ref="E18">Common_InputFunctions.Utility_LookupValueInTableNumber($E$7, Table_SourceData_Dairy_WjCowsHeifers[Breed],Table_SourceData_Dairy_WjCowsHeifers[Milking cows])</f>
@@ -14239,7 +14246,7 @@
     </row>
     <row r="19" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E19" s="67" cm="1">
         <f t="array" ref="E19">Table_SourceData_Dairy_LWGj[Milking cows]</f>
@@ -14485,7 +14492,7 @@
     <row r="33" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="D33" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R33" s="7"/>
     </row>
@@ -14516,30 +14523,30 @@
     </row>
     <row r="36" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36" s="54" cm="1">
-        <f t="array" ref="E36">Common_InputFunctions.Utility_LookupValueInTableNumber(E35,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="F36" s="54" cm="1">
-        <f t="array" ref="F36">Common_InputFunctions.Utility_LookupValueInTableNumber(F35,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="G36" s="54" cm="1">
-        <f t="array" ref="G36">Common_InputFunctions.Utility_LookupValueInTableNumber(G35,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>281</v>
-      </c>
-      <c r="H36" s="54" cm="1">
-        <f t="array" ref="H36">Common_InputFunctions.Utility_LookupValueInTableNumber(H35,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="I36" s="54" cm="1">
-        <f t="array" ref="I36">Common_InputFunctions.Utility_LookupValueInTableNumber(I35,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>281</v>
+        <v>16</v>
+      </c>
+      <c r="E36" s="54">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="54">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="G36" s="54">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="H36" s="54">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="I36" s="54">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -14548,27 +14555,27 @@
     </row>
     <row r="37" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="E37" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
-        <v>0.75</v>
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="F37" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
-        <v>0.75</v>
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="G37" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
-        <v>0.75</v>
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="H37" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
-        <v>0.75</v>
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="I37" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
-        <v>0.75</v>
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>93</v>
@@ -14579,32 +14586,6 @@
       <c r="R37" s="7"/>
     </row>
     <row r="38" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E38" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
-        <v>0.2</v>
-      </c>
-      <c r="F38" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
-        <v>0.2</v>
-      </c>
-      <c r="G38" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
-        <v>0.2</v>
-      </c>
-      <c r="H38" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
-        <v>0.2</v>
-      </c>
-      <c r="I38" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
-        <v>0.2</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -14612,56 +14593,83 @@
     </row>
     <row r="39" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
+      <c r="D39" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>148</v>
+      </c>
       <c r="R39" s="7"/>
     </row>
     <row r="40" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="H40" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="I40" s="41" t="s">
-        <v>148</v>
-      </c>
+      <c r="D40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="67">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="F40" s="67">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="G40" s="67">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="H40" s="67">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="I40" s="67">
+        <f>'Constants - Dairy'!$D$160</f>
+        <v>0.75</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="R40" s="7"/>
     </row>
     <row r="41" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="47"/>
       <c r="D41" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="67" cm="1">
-        <f t="array" ref="E41">Common_InputFunctions.Utility_LookupValueInTableNumber(E40,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="F41" s="67" cm="1">
-        <f t="array" ref="F41">Common_InputFunctions.Utility_LookupValueInTableNumber(F40,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="G41" s="67" cm="1">
-        <f t="array" ref="G41">Common_InputFunctions.Utility_LookupValueInTableNumber(G40,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>281</v>
-      </c>
-      <c r="H41" s="67" cm="1">
-        <f t="array" ref="H41">Common_InputFunctions.Utility_LookupValueInTableNumber(H40,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>365</v>
-      </c>
-      <c r="I41" s="67" cm="1">
-        <f t="array" ref="I41">Common_InputFunctions.Utility_LookupValueInTableNumber(I40,Table_SourceData_Dairy_Duration[Animal class j],Table_SourceData_Dairy_Duration[Duration (weaned)])</f>
-        <v>281</v>
+        <v>101</v>
+      </c>
+      <c r="E41" s="67">
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
+      </c>
+      <c r="F41" s="67">
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
+      </c>
+      <c r="G41" s="67">
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="67">
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
+      </c>
+      <c r="I41" s="67">
+        <f>'Constants - Dairy'!$D$153</f>
+        <v>0.2</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -14669,55 +14677,12 @@
       <c r="R41" s="7"/>
     </row>
     <row r="42" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="F42" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="G42" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="H42" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="I42" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="R42" s="7"/>
     </row>
     <row r="43" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="F43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="G43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="H43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="I43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="R43" s="7"/>
@@ -14770,10 +14735,10 @@
     </row>
     <row r="49" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>9</v>
@@ -14815,19 +14780,19 @@
     </row>
     <row r="54" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="55" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R54" s="7"/>
     </row>
     <row r="55" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E55" s="124">
         <f>'Constants - Dairy'!$D$221/100</f>
@@ -14838,13 +14803,13 @@
         <v>0.04</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R55" s="7"/>
     </row>
     <row r="56" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E56" s="124">
         <f>'Constants - Dairy'!$D$227/100</f>
@@ -14855,7 +14820,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R56" s="7"/>
     </row>
@@ -15124,28 +15089,18 @@
       <c r="M178" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E10:M10 E24:M25 E28:M29 O43:P43 N44 J85:J90 K89:M89 K95:M95 F98 J101:J106 K105:M105 K110:M110 K114:M114 K123:M123">
-    <cfRule type="cellIs" dxfId="8" priority="30" operator="lessThan">
+  <conditionalFormatting sqref="E10:M10 E24:M25 E28:M29 E36:J37 K36:M38 E40:K41 L41:M43 K42 O43:P43 N44 J85:J90 K89:M89 K95:M95 F98 J101:J106 K105:M105 K110:M110 K114:M114 K123:M123">
+    <cfRule type="cellIs" dxfId="6" priority="30" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:M15">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18:M19">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E36:M38">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E41:M43">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15169,7 +15124,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations disablePrompts="1" count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E109" xr:uid="{AF94BFC8-A9BD-4286-932B-111409BF1EB6}">
       <formula1>INDIRECT("Table_SourceData_Dairy_CropProdSystems[Production system]")</formula1>
     </dataValidation>
@@ -15215,7 +15170,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K1"/>
     </row>
@@ -15381,7 +15336,7 @@
         <v>107</v>
       </c>
       <c r="M17" s="100" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15422,67 +15377,67 @@
     </row>
     <row r="19" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="54">
-        <f>'Input - Dairy'!$E$37</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method1,2,2)</f>
         <v>0.75</v>
       </c>
       <c r="E19" s="54">
-        <f>'Input - Dairy'!$F$37</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method1,2,3)</f>
         <v>0.75</v>
       </c>
       <c r="F19" s="54">
-        <f>'Input - Dairy'!$G$37</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method1,2,4)</f>
         <v>0.75</v>
       </c>
       <c r="G19" s="54">
-        <f>'Input - Dairy'!$H$37</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method1,2,5)</f>
         <v>0.75</v>
       </c>
       <c r="H19" s="54">
-        <f>'Input - Dairy'!$I$37</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method1,2,6)</f>
         <v>0.75</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M19" s="54">
-        <f>'Input - Dairy'!$E$42</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method2,2,2)</f>
         <v>0.75</v>
       </c>
       <c r="N19" s="54">
-        <f>'Input - Dairy'!$F$42</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method2,2,3)</f>
         <v>0.75</v>
       </c>
       <c r="O19" s="54">
-        <f>'Input - Dairy'!$G$42</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method2,2,4)</f>
         <v>0.75</v>
       </c>
       <c r="P19" s="54">
-        <f>'Input - Dairy'!$H$42</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method2,2,5)</f>
         <v>0.75</v>
       </c>
       <c r="Q19" s="54">
-        <f>'Input - Dairy'!$I$42</f>
+        <f>INDEX(X_Table_Dairy_Diet_Method2,2,6)</f>
         <v>0.75</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="101" t="s">
+        <v>175</v>
+      </c>
+      <c r="M21" s="101" t="s">
         <v>177</v>
-      </c>
-      <c r="M21" s="101" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="100" t="s">
+        <v>176</v>
+      </c>
+      <c r="M22" s="100" t="s">
         <v>178</v>
-      </c>
-      <c r="M22" s="100" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15652,7 +15607,7 @@
         <v>Input</v>
       </c>
       <c r="I37" s="122" t="str">
-        <f>'Input - Dairy'!$E$49</f>
+        <f>X_Cell_Dairy_MilkProductionUnit</f>
         <v>Litres of milk</v>
       </c>
       <c r="M37" s="122" t="str" cm="1">
@@ -15780,12 +15735,12 @@
     <row r="41" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="101" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="100" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15823,24 +15778,24 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="101" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M47" s="101" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="100" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M48" s="100" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15893,7 +15848,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M50" s="54" cm="1">
         <f t="array" ref="M50">EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids(D45,R39,R40)</f>
@@ -15912,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16008,7 +15963,7 @@
         <v>Input</v>
       </c>
       <c r="I64" s="122" t="str">
-        <f>'Input - Dairy'!$E$49</f>
+        <f>X_Cell_Dairy_MilkProductionUnit</f>
         <v>Litres of milk</v>
       </c>
     </row>
@@ -16129,7 +16084,7 @@
     <row r="71" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="101" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16172,24 +16127,24 @@
         <v>0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="101" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M77" s="101" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="100" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M78" s="100" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16417,18 +16372,18 @@
     <row r="96" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="M97" s="101" t="s">
         <v>166</v>
-      </c>
-      <c r="M97" s="101" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="M98" s="100" t="s">
         <v>167</v>
-      </c>
-      <c r="M98" s="100" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16514,18 +16469,18 @@
     <row r="101" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="M102" s="101" t="s">
         <v>170</v>
-      </c>
-      <c r="M102" s="101" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="M103" s="100" t="s">
         <v>171</v>
-      </c>
-      <c r="M103" s="100" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16615,12 +16570,12 @@
     <row r="106" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="107" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="101" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="100" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16676,10 +16631,10 @@
     </row>
     <row r="113" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D113" s="100" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M113" s="100" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="114" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16848,18 +16803,18 @@
     <row r="128" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="129" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="101" t="s">
+        <v>219</v>
+      </c>
+      <c r="M129" s="101" t="s">
         <v>221</v>
-      </c>
-      <c r="M129" s="101" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="130" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D130" s="100" t="s">
+        <v>220</v>
+      </c>
+      <c r="M130" s="100" t="s">
         <v>222</v>
-      </c>
-      <c r="M130" s="100" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="131" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17181,7 +17136,7 @@
     </row>
     <row r="158" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="100" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17230,18 +17185,18 @@
     <row r="161" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="162" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="101" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M162" s="101" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="100" t="s">
+        <v>224</v>
+      </c>
+      <c r="M163" s="100" t="s">
         <v>226</v>
-      </c>
-      <c r="M163" s="100" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="164" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17329,18 +17284,18 @@
     <row r="166" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="167" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="101" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M167" s="101" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="168" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M168" s="100" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="169" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17428,12 +17383,12 @@
     <row r="171" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="172" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D172" s="101" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="173" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="174" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17461,10 +17416,10 @@
     <row r="176" spans="4:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="177" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D177" s="101" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M177" s="101" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="178" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17473,10 +17428,10 @@
         <v>▲ Back to top</v>
       </c>
       <c r="D178" s="100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M178" s="100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="179" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17564,7 +17519,7 @@
     <row r="181" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="182" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="103" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E182" s="104">
         <f>SUM(D180:H180)</f>
@@ -17575,7 +17530,7 @@
         <v>t CH4</v>
       </c>
       <c r="M182" s="103" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N182" s="104">
         <f>SUM(M180:Q180)</f>
@@ -17788,7 +17743,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21991,7 +21946,7 @@
     </row>
     <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="39" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E142" s="39" t="s">
         <v>89</v>
@@ -22681,7 +22636,7 @@
         <v>8</v>
       </c>
       <c r="E206" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
@@ -22712,10 +22667,10 @@
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212" s="39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E212" s="39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
@@ -22861,49 +22816,49 @@
         <v>50</v>
       </c>
       <c r="E231" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="F231" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="G231" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="F231" s="38" t="s">
+      <c r="H231" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="G231" s="39" t="s">
+      <c r="I231" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="H231" s="39" t="s">
+      <c r="J231" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="I231" s="39" t="s">
+      <c r="K231" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="J231" s="39" t="s">
+      <c r="L231" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="K231" s="39" t="s">
+      <c r="M231" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="L231" s="39" t="s">
+      <c r="N231" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="M231" s="39" t="s">
+      <c r="O231" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="N231" s="39" t="s">
+      <c r="P231" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="O231" s="39" t="s">
+      <c r="Q231" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="P231" s="39" t="s">
+      <c r="R231" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="Q231" s="39" t="s">
+      <c r="S231" s="39" t="s">
         <v>214</v>
-      </c>
-      <c r="R231" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="S231" s="39" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -24186,10 +24141,10 @@
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D257" s="39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E257" s="39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
@@ -24712,10 +24667,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABDAG8AdwBzACAAYQBuAGQAIABIAGUAaQBmAGUAcgBzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgAFwAdQAwADAAMgA3AFIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAXAB1ADAAMAAyADcARABhAGkAcgB5ACAAQQB1AHMAdAByAGEAbABpAGEAIABbADEAXQBcAHUAMAAwADIANwAgAGEAbgBkACAAaQBzACAAbgBvAHQAIAB1AHMAZQBkACAAaQBuACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAZABpAHUAbQAgAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADUANQAwACwAIAAzADgAMAAsACAAMQA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABhAHIAZwBlACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AbABzAHQAZQBpAG4ALQBGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADUAMAAsACAANAA1ADAALAAgADEAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBpAGUAcwBpAGEAbgAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANQAwADAALAAgADMANQAwACwAIAAxADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQBcACIALAAgADQAMAAwACwAIAAyADcANQAsACAAMQAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBlAHIAcwBlAHkAIABjAHIAbwBzAHMAYgByAGUAZABcACIALAAgADQANQAwACwAIAAzADEANQAsACAAMQAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB5AHIAcwBoAGkAcgBlAFwAIgAsACAANQA0ADAALAAgADMANwA1ACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHUAZQByAG4AcwBlAHkAXAAiACwAIAA0ADgAMAAsACAAMwAzADUALAAgADEANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBvAHcAbgAgAFMAdwBpAHMAcwBcACIALAAgADYAMAAwACwAIAA0ADEANQAsACAAMQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBsAGwAYQB3AGEAcgByAGEALwBBAHUAcwBzAGkAZQAgAFIAZQBkAFwAIgAsACAANQA1ADAALAAgADMANwA1ACwAIAAxADUAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEIAdQBsAGwAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgADUAOQAwACwAIAA1ADkAMAAsACAANQA5ADAALAAgADcANwAwACwAIAA3ADcAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAagA9ADMALAA1ADsAIABOAFAAVwBqAD0AMwAsADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAAoAFYAUwBqAD0AMwAsADUAKQBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIABFAHgAYwByAGUAdABlAGQAIAAoAE4AUABXAGoAPQAzACwANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMQA3ADYALAAgADAALgAyADYAOAA1ACwAIAAwAC4AMAAxADMANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAXAB1ADAAMAAzAGMAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAxADAALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgA3ADIALAAgADAALgA3ADYALAAgADAALgA4ACwAIAAwAC4ANwA4ACwAIAAwAC4ANwA0ACwAIAAwAC4ANgA5ACwAIAAwAC4ANwAzACwAIAAwAC4ANwA2ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAIAAoAGEAKQBcACIALAAgADAALgAxADUALAAgADAALgAxADgALAAgADAALgA1ADAALAAgADAALgAyADQALAAgADAALgAxADcALAAgADAALgAxADMALAAgADAALgAxADcALAAgADAALgAxADgALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBtADsAIABGAHIAYQBjAEcAQQBTAE0AbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkACkAXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQA0ACAAUABhAHMAdAB1AHIAZQBcACIALAAgADAALAAgADAALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgADAALgAwADcALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAUABhAGQAZABvAGMAawBcACIALAAgADAALAAgADAALgAyACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAzACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBQAFcARQBOAFQARQBSAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAwAC4AMAAxADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIABcAHUAMAAwADIANwBBAG4AbgB1AGEAbAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaQBtAGUAIABzAHAAZQBuAHQAIABwAGUAcgAgAGEAcgBlAGEAXAB1ADAAMAAyADcAIAByAG8AdwAgAGEAcwAgAHQAaABpAHMAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AIABpAHMAIABpAG4AIAB0AGgAZQAgAHQAYQBiAGwAZQAgAHQAaQB0AGwAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcgBlAGEAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAUwBoAGUAZABcACIALAAgAFwAIgBGAGUAZQBkAHAAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADEAOgAgAEcAcgBhAHoAZQBkACAATwBuAGwAeQBcACIALAAgADAALgA4ADkALAAgADAALgAxADEALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAyADoAIABPAG4AIABmAGUAZQBkAHAAYQBkACAAZgBvAHIAIABcAHUAMAAwADMAYwAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAXAB1ADAAMAAzAGMAMwAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA3ADkALAAgADAALgAxADEALAAgADAALgAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAzADoAIABQAGEAcwB0AHUAcgBlAC0AZwByAGEAegBlAGQAIAAzAC0AOQAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA1ADMANAAsACAAMAAuADEAMQAsACAAMAAuADMANQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAANAA6ACAAWgBlAHIAbwAgAGcAcgBhAHoAaQBuAGcAXAAiACwAIAAwACwAIAAwAC4AMQAxACwAIAAwAC4AOAA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQAgAHkAZQBhAHIAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAFwAbgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAUABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQATQBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA3ADUAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBcAG4ATgBlAHQAIABlAG4AZQByAGcAeQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAvACAAawBnACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAwADUANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AFwAbgBHAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAZAByAHkAIABtAGEAdAB0AGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcARQBDAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEoAIAAvACAAawBnAEQATQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADEAOAAuADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBcAG4ARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIAB1AHMAZQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAOAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAXwBvAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMQAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARABlAGYAYQB1AGwAdAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAdwBoAGUAbgAgAG0AYQBuAHUAcgBlACAAaQBzACAAZQB4AGMAcgBlAHQAZQBkACAAdABvACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAKABtAD0AMQA0ACkALgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAegBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXABuAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgAgAEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0AC4AMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4AUAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAEMAXwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAzAC4AMwApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADMAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABEAGEAaQByAHkAIABDAGEAdAB0AGwAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9ACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAMQAyADQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADEAMgA0ACAAPQAgAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADEAMgA0ACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABkAGEAeQBzACkAXABuAE4AXwBqADMANQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAaABlAGEAZAApAFwAbgBNAF8AagAzADUAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBEAF8AagAzADUAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAZABhAHkAcwApAFwAbgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAxADIANAAsACAATQBfAGoAMQAyADQALAAgAEQAXwBqADEAMgA0ACwAIABOAF8AagAzADUALAAgAE0AXwBqADMANQAsACAARABfAGoAMwA1ACwAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAsAFwAbgAgACAAIAAgACgAKABOAF8AagAxADIANAAgACoAIABNAF8AagAxADIANAAgACoAIABEAF8AagAxADIANAApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AXwBqADMANQAgACoAIABEAF8AagAzADUAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgACoAIABEAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAEQAUABXAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAUABXAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABQAFcAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAxADIANABcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAzADUAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABQAFcAXwBqADMANQBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEQAUABXAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -24910,7 +24876,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -24919,18 +24885,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
@@ -24938,7 +24904,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24957,21 +24923,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9374AE3A-8F48-4E24-958F-C4F43063A3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59C64C6-9746-403D-A9DA-6885C9D0B99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1830" yWindow="1065" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -57,7 +57,9 @@
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -222,6 +224,31 @@
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title">_xlfn.LAMBDA("Table 5.12 Additional symbols used in algorithms for manure related emissions")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable">_xlfn.LAMBDA("MMS")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Cattle, for manufacturing beef","Australia";"Cattle, for prime beef","NSW";"Cattle, weaners","NT";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Title">_xlfn.LAMBDA("Beef cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Chickens","Australia"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Title">_xlfn.LAMBDA("Chickens products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Dairy cows","VIC"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Title">_xlfn.LAMBDA("Dairy cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Pigs","Australia"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Title">_xlfn.LAMBDA("Pigs products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Sheep, for mutton","Australia";"Sheep, for prime lamb","NSW";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Title">_xlfn.LAMBDA("Sheep products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Vairable">_xlfn.LAMBDA("")</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentation">_xlfn.LAMBDA(_xlpm.N_j124,_xlpm.M_j124,_xlpm.D_j124,_xlpm.N_j35,_xlpm.M_j35,_xlpm.D_j35,_xlpm.MPW_ENTERIC_j35, ((_xlpm.N_j124 * _xlpm.M_j124 * _xlpm.D_j124) + (_xlpm.N_j35 * _xlpm.M_j35 * _xlpm.D_j35) + (_xlpm.N_j35 * _xlpm.MPW_ENTERIC_j35 * _xlpm.D_j35)) * 10 ^ -3)</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"N_j124","number of dairy cattle in classes j=1,2,4","head","Input";"M_j124","daily enteric methane production for classes j=1,2,4","kg CH4/head/day","Calculated from 3.3.1.1 (2)";"D_j124","duration of stay on the farm for classes j=1,2,4","days","Input";"N_j35","number of dairy cattle in classes j=3,5","head","Input";"M_j35","daily enteric methane production for weaned classes j=3,5","kg CH4/head/day","Calculated from 3.3.1.1 (2)";"D_j35","duration of stay on the farm for weaned classes j=3,5","days","Input";"DPW_j35","duration of stay on the farm for pre-weaned heifer and bull calves","days","Input";"MPW_ENTERIC_j35","daily methane production for pre-weaned heifer and bull calves","kg CH4/head/day","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentation_LatexEquation">_xlfn.LAMBDA("E_{enteric}=\sum\nolimits_j((N_{j=1,2,4}\times M_{j=1,2,4}\times D_{j=1,2,4})+(N_{j=3,5}\times M_{j=3,5}\times D_{j=3,5})+(N_{j=3,5}\times MPW_{ENTERIC,j=3,5}\times D_{j=3,5}))\times 10^{-3}")</definedName>
@@ -259,7 +286,7 @@
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__4_AdditionalIntakeForMilkProduction_Variable">_xlfn.LAMBDA("MI_j")</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__4_AdditionalIntakeForMilkProduction_Variation">_xlfn.LAMBDA("VARATION ON SOURCE: Added milk production unit variable to allow for use of either milk solids or litres of milk.")</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids">_xlfn.LAMBDA(_xlpm.MS_j,_xlpm.FC_j,_xlpm.PC_j, _xlpm.MS_j / (0.01 * (_xlpm.FC_j + _xlpm.PC_j)))</definedName>
-    <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MPU","input milk production unit","","Input";"MS_j","daily production of milk solids","kg MS/head/day","Input";"FC_j","fat content in fat and protein corrected milk","per cent","Constant";"PC_j","protein content in fat and protein corrected milk","per cent","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MPU","input milk production unit","","Input";"MS_j","daily production of milk solids","kg MS/head/day","Input";"FC_j","fat content in fat and protein corrected milk","per cent","Input";"PC_j","protein content in fat and protein corrected milk","per cent","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments_Method2">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MPU","milk production unit","","Input";"MS_j","daily production of milk solids","kg MS/head/day","Input";"FC_j","fat content in fat and protein corrected milk","per cent","Input";"PC_j","protein content in fat and protein corrected milk","per cent","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_LatexEquation">_xlfn.LAMBDA("MP_j=\frac{MS_j}{0.01\times (FC_j+PC_j)}")</definedName>
     <definedName name="EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_NIRReference">_xlfn.LAMBDA("")</definedName>
@@ -380,6 +407,12 @@
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoff_Unit">_xlfn.LAMBDA("Dimensionless")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoff_Variable">_xlfn.LAMBDA("Frac_LEACH_MS")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoff_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Data">_xlfn.LAMBDA(0.02)</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Source">_xlfn.LAMBDA("VEERG 2026: 4.3.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Title">_xlfn.LAMBDA("Fraction of nitrogen lost through leaching and runoff for solid storage MMS only")</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Unit">_xlfn.LAMBDA("Fraction")</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Variable">_xlfn.LAMBDA("Frac_LEACH_MS")</definedName>
+    <definedName name="SourceData_Dairy.SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoffSolidStorage_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Area","Pasture","Milking Shed","Feedpad";"System 1: Grazed Only",0.89,0.11,0;"System 2: On feedpad for &lt;10 hr/day for &lt;3 months/year",0.79,0.11,0.1;"System 3: Pasture-grazed 3-9 months/year",0.534,0.11,0.356;"System 4: Zero grazing",0,0.11,0.89}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.3.10")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Title">_xlfn.LAMBDA("Table A.1.3.10: Dairy cattle - Fraction of volatile solids voided to each manure management system (fraction) (MMSjm)")</definedName>
@@ -475,10 +508,6 @@
     <definedName name="X_Cell_Dairy_Breed">'Input - Dairy'!$E$7</definedName>
     <definedName name="X_Cell_Dairy_MilkProductionAmount">'Input - Dairy'!$E$52</definedName>
     <definedName name="X_Cell_Dairy_MilkProductionUnit">'Input - Dairy'!$E$49</definedName>
-    <definedName name="X_Cell_Dairy_MilkSolidsFatContent_Method1">'Input - Dairy'!$E$55</definedName>
-    <definedName name="X_Cell_Dairy_MilkSolidsFatContent_Method2">'Input - Dairy'!$F$55</definedName>
-    <definedName name="X_Cell_Dairy_MilkSolidsProteinContent_Method1">'Input - Dairy'!$F$56</definedName>
-    <definedName name="X_Cell_Dairy_MilkSolidsProteinContent_Method2">'Input - Dairy'!$F$56</definedName>
     <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$25</definedName>
     <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$31</definedName>
     <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$24</definedName>
@@ -503,6 +532,7 @@
     <definedName name="X_Table_Dairy_HerdMovement">'Input - Dairy'!$D$9:$I$10</definedName>
     <definedName name="X_Table_Dairy_Liveweight_Method1">'Input - Dairy'!$D$13:$I$15</definedName>
     <definedName name="X_Table_Dairy_Liveweight_Method2">'Input - Dairy'!$D$17:$I$19</definedName>
+    <definedName name="X_Table_Dairy_MilkSolidAttributes">'Input - Dairy'!$D$54:$F$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10205,7 +10235,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="850" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="836" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -15611,15 +15641,15 @@
         <v>Litres of milk</v>
       </c>
       <c r="M37" s="122" t="str" cm="1">
-        <f t="array" ref="M37:N40">_xlfn.CHOOSECOLS(EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments(),1,2)</f>
+        <f t="array" ref="M37:N40">_xlfn.CHOOSECOLS(EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments_Method2(),1,2)</f>
         <v>MPU</v>
       </c>
       <c r="N37" s="121" t="str">
-        <v>input milk production unit</v>
+        <v>milk production unit</v>
       </c>
       <c r="O37" s="123"/>
       <c r="P37" s="122" t="str" cm="1">
-        <f t="array" ref="P37:Q40">_xlfn.CHOOSECOLS(EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments(),3,4)</f>
+        <f t="array" ref="P37:Q40">_xlfn.CHOOSECOLS(EntericMethane_Dairy_Equations.VEERG_3_3_1_1__5_MilkProductionFromMilkSolids_Arguments_Method2(),3,4)</f>
         <v/>
       </c>
       <c r="Q37" s="120" t="str">
@@ -15671,11 +15701,11 @@
       <c r="G39" s="122" t="str">
         <v>per cent</v>
       </c>
-      <c r="H39" s="118" t="str">
-        <v>Constant</v>
+      <c r="H39" s="120" t="str">
+        <v>Input</v>
       </c>
       <c r="I39" s="122">
-        <f>'Input - Dairy'!$E$55*100</f>
+        <f>INDEX(X_Table_Dairy_MilkSolidAttributes,2,2)*100</f>
         <v>4</v>
       </c>
       <c r="M39" s="122" t="str">
@@ -15688,11 +15718,11 @@
       <c r="P39" s="122" t="str">
         <v>per cent</v>
       </c>
-      <c r="Q39" s="118" t="str">
-        <v>Constant</v>
+      <c r="Q39" s="120" t="str">
+        <v>Input</v>
       </c>
       <c r="R39" s="122">
-        <f>'Input - Dairy'!$F$55*100</f>
+        <f>INDEX(X_Table_Dairy_MilkSolidAttributes,2,3)*100</f>
         <v>4</v>
       </c>
     </row>
@@ -15707,11 +15737,11 @@
       <c r="G40" s="122" t="str">
         <v>per cent</v>
       </c>
-      <c r="H40" s="118" t="str">
-        <v>Constant</v>
+      <c r="H40" s="120" t="str">
+        <v>Input</v>
       </c>
       <c r="I40" s="122">
-        <f>'Input - Dairy'!$E$56*100</f>
+        <f>INDEX(X_Table_Dairy_MilkSolidAttributes,3,2)*100</f>
         <v>3.3000000000000003</v>
       </c>
       <c r="M40" s="122" t="str">
@@ -15724,11 +15754,11 @@
       <c r="P40" s="122" t="str">
         <v>per cent</v>
       </c>
-      <c r="Q40" s="118" t="str">
-        <v>Constant</v>
+      <c r="Q40" s="120" t="str">
+        <v>Input</v>
       </c>
       <c r="R40" s="122">
-        <f>'Input - Dairy'!$F$56*100</f>
+        <f>INDEX(X_Table_Dairy_MilkSolidAttributes,3,3)*100</f>
         <v>3.3000000000000003</v>
       </c>
     </row>
@@ -24678,7 +24708,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABDAG8AdwBzACAAYQBuAGQAIABIAGUAaQBmAGUAcgBzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgAFwAdQAwADAAMgA3AFIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACwAIABhAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAGkAcwAgAGMAbwBuAHMAaQBzAHQAZQBuAHQAbAB5ACAAXAB1ADAAMAAyADcARABhAGkAcgB5ACAAQQB1AHMAdAByAGEAbABpAGEAIABbADEAXQBcAHUAMAAwADIANwAgAGEAbgBkACAAaQBzACAAbgBvAHQAIAB1AHMAZQBkACAAaQBuACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAZABpAHUAbQAgAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADUANQAwACwAIAAzADgAMAAsACAAMQA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABhAHIAZwBlACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AbABzAHQAZQBpAG4ALQBGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADUAMAAsACAANAA1ADAALAAgADEAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBpAGUAcwBpAGEAbgAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANQAwADAALAAgADMANQAwACwAIAAxADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQBcACIALAAgADQAMAAwACwAIAAyADcANQAsACAAMQAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBlAHIAcwBlAHkAIABjAHIAbwBzAHMAYgByAGUAZABcACIALAAgADQANQAwACwAIAAzADEANQAsACAAMQAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB5AHIAcwBoAGkAcgBlAFwAIgAsACAANQA0ADAALAAgADMANwA1ACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHUAZQByAG4AcwBlAHkAXAAiACwAIAA0ADgAMAAsACAAMwAzADUALAAgADEANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBvAHcAbgAgAFMAdwBpAHMAcwBcACIALAAgADYAMAAwACwAIAA0ADEANQAsACAAMQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBsAGwAYQB3AGEAcgByAGEALwBBAHUAcwBzAGkAZQAgAFIAZQBkAFwAIgAsACAANQA1ADAALAAgADMANwA1ACwAIAAxADUAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEIAdQBsAGwAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAYgByAGUAZQBkAHMAXAAiACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcAKQAgACgATABXAEcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAFcARwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgADUAOQAwACwAIAA1ADkAMAAsACAANQA5ADAALAAgADcANwAwACwAIAA3ADcAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAHQAYQAgAGYAbwByACAAcAByAGUAIAAtACAAdwBlAGEAbgBlAGQAIABjAGEAbAB2AGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAagA9ADMALAA1ADsAIABOAFAAVwBqAD0AMwAsADUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAAoAFYAUwBqAD0AMwAsADUAKQBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIABFAHgAYwByAGUAdABlAGQAIAAoAE4AUABXAGoAPQAzACwANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMQA3ADYALAAgADAALgAyADYAOAA1ACwAIAAwAC4AMAAxADMANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAXAB1ADAAMAAzAGMAMQBcACIALAAgADAALgAwADIAMAA0ACwAIAAwAC4AMwAwADAAMwAsACAAMAAuADAAMAA5ADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AQwBGAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAxADAALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgA3ADIALAAgADAALgA3ADYALAAgADAALgA4ACwAIAAwAC4ANwA4ACwAIAAwAC4ANwA0ACwAIAAwAC4ANgA5ACwAIAAwAC4ANwAzACwAIAAwAC4ANwA2ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMAA1ACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAIAAoAGEAKQBcACIALAAgADAALgAxADUALAAgADAALgAxADgALAAgADAALgA1ADAALAAgADAALgAyADQALAAgADAALgAxADcALAAgADAALgAxADMALAAgADAALgAxADcALAAgADAALgAxADgALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAYQBuAGQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBtADsAIABGAHIAYQBjAEcAQQBTAE0AbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkACkAXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQA0ACAAUABhAHMAdAB1AHIAZQBcACIALAAgADAALAAgADAALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgADAALgAwADcALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAUABhAGQAZABvAGMAawBcACIALAAgADAALAAgADAALgAyACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAzACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBQAFcARQBOAFQARQBSAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAwAC4AMAAxADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAMAAuADAAMgAwADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUgBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABNAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFIAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBSAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzACwAIABhAG4AZAAgAGgAbwB1AHMAZQAgAGMAbwB3AHMAXAAiACwAIAAxAC4AMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAGUAcwBcACIALAAgADEALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABFAHgAYwBsAHUAZABlAGQAIABcAHUAMAAwADIANwBBAG4AbgB1AGEAbAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaQBtAGUAIABzAHAAZQBuAHQAIABwAGUAcgAgAGEAcgBlAGEAXAB1ADAAMAAyADcAIAByAG8AdwAgAGEAcwAgAHQAaABpAHMAIABpAG4AZgBvAHIAbQBhAHQAaQBvAG4AIABpAHMAIABpAG4AIAB0AGgAZQAgAHQAYQBiAGwAZQAgAHQAaQB0AGwAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcgBlAGEAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAUwBoAGUAZABcACIALAAgAFwAIgBGAGUAZQBkAHAAYQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADEAOgAgAEcAcgBhAHoAZQBkACAATwBuAGwAeQBcACIALAAgADAALgA4ADkALAAgADAALgAxADEALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAyADoAIABPAG4AIABmAGUAZQBkAHAAYQBkACAAZgBvAHIAIABcAHUAMAAwADMAYwAxADAAIABoAHIALwBkAGEAeQAgAGYAbwByACAAXAB1ADAAMAAzAGMAMwAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA3ADkALAAgADAALgAxADEALAAgADAALgAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAzADoAIABQAGEAcwB0AHUAcgBlAC0AZwByAGEAegBlAGQAIAAzAC0AOQAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA1ADMANAAsACAAMAAuADEAMQAsACAAMAAuADMANQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAANAA6ACAAWgBlAHIAbwAgAGcAcgBhAHoAaQBuAGcAXAAiACwAIAAwACwAIAAwAC4AMQAxACwAIAAwAC4AOAA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAxACAAQQBuAGUAcgBvAGIAaQBjACAATABhAGcAbwBvAG4AXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAXAAiACwAIAAwACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADMAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAA6ACAARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAHMAXAAiACwAIAAwACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0ANAAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABhAHkAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQwBvAG4AdgBlAHIAdABlAGQAIABmAHIAZQBlACAAdABlAHgAdAAgAGkAbgAgAGQAbwBjAHUAbQBlAG4AdAAgAHQAbwAgAHQAYQBiAGwAZQAsACAAbQBhAHQAYwBoAGkAbgBnACAAbABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAIABuAGEAbQBlAHMALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKABwAHIAZQAtAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABjAG8AdwBzAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQAgAHkAZQBhAHIAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAFwAbgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAUABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQATQBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA3ADUAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBcAG4ATgBlAHQAIABlAG4AZQByAGcAeQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAvACAAawBnACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAwADUANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AFwAbgBHAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAZAByAHkAIABtAGEAdAB0AGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcARQBDAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEoAIAAvACAAawBnAEQATQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADEAOAAuADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBcAG4ARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIAB1AHMAZQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAOAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAXwBvAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMQAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARABlAGYAYQB1AGwAdAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAdwBoAGUAbgAgAG0AYQBuAHUAcgBlACAAaQBzACAAZQB4AGMAcgBlAHQAZQBkACAAdABvACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAKABtAD0AMQA0ACkALgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAegBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXABuAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgAgAEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0AC4AMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4AUAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAEMAXwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAzAC4AMwApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADMAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABEAGEAaQByAHkAIABDAGEAdAB0AGwAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9ACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAMQAyADQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADEAMgA0ACAAPQAgAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADEAMgA0ACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABkAGEAeQBzACkAXABuAE4AXwBqADMANQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAaABlAGEAZAApAFwAbgBNAF8AagAzADUAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBEAF8AagAzADUAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAZABhAHkAcwApAFwAbgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAxADIANAAsACAATQBfAGoAMQAyADQALAAgAEQAXwBqADEAMgA0ACwAIABOAF8AagAzADUALAAgAE0AXwBqADMANQAsACAARABfAGoAMwA1ACwAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAsAFwAbgAgACAAIAAgACgAKABOAF8AagAxADIANAAgACoAIABNAF8AagAxADIANAAgACoAIABEAF8AagAxADIANAApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AXwBqADMANQAgACoAIABEAF8AagAzADUAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgACoAIABEAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAEQAUABXAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAUABXAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABQAFcAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAxADIANABcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAzADUAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABQAFcAXwBqADMANQBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEQAUABXAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABhACAAcwBlAHAAYQByAGEAdABlACAAaABhAG4AZABsAGkAbgBnACAAbwBmACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGQAdQByAGEAdABpAG8AbgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALABcAG4AIAAgACAAIAAyADAALgA3ACAAKgAgAEkAXwBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGEAcgBtAGwAZQB5ACAAZQB0ACAAYQBsAC4AIAAoADIAMAAxADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AMgAwAC4ANwBcAFwAdABpAG0AZQBzACAASQBfAGoAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcAG4AVwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAEwAVwBHAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE0AUgBfAGoAIAA9ACAAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAE0ASQBfAGoAIAA9ACAAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGoALAAgAEwAVwBHAF8AagAsACAATQBSAF8AagAsACAATQBJAF8AagAsAFwAbgAgACAAIAAgACgAMQAuADEAOAA1ACAAKwAgADAALgAwADAANAA1ADQAIAAqACAAVwBfAGoAIAAtACAAMAAuADAAMAAwADAAMAAyADYAIAAqACAAVwBfAGoAIABeACAAMgAgACsAIAAwAC4AMwAxADUAIAAqACAATABXAEcAXwBqACkAIABeACAAMgAgACoAIABNAFIAXwBqACAAKwAgAE0ASQBfAGoAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBfAGoAPQAoADEALgAxADgANQArADAALgAwADAANAA1ADQAXABcAHQAaQBtAGUAcwAgAFcAXwBqAC0AMAAuADAAMAAwADAAMAAyADYAXABcAHQAaQBtAGUAcwAgAFcAXwBqAF4AMgArADAALgAzADEANQBcAFwAdABpAG0AZQBzACAATABXAEcAXwBqACkAXgAyAFwAXAB0AGkAbQBlAHMAIABNAFIAXwBqACsATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdABcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAFcARwBfAGoAXAAiACwAIABcACIAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACwAIABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBSAF8AagBcACIALAAgAFwAIgBpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ASQBfAGoAXAAiACwAIABcACIAYQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA0ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBNAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ASQBfAGoAPQAoAE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQApAC8AKABHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagApAFwAbgBNAFAAXwBqACAAPQAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABMAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4ARQAgAD0AIABuAGUAdAAgAGUAbgBlAHIAZwB5ACAAKABNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawApAFwAbgBHAEUAQwAgAD0AIABnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIAAoAE0ASgAvAGsAZwBEAE0AKQBcAG4AawAgAD0AIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4AcQBtAF8AagAgAD0AIABtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBQAF8AagAsACAATgBFACwAIABHAEUAQwAsACAAawAsACAAcQBtAF8AagAsAFwAbgAgACAAIAAgACgATQBQAF8AagAgACoAIAAxAC4AMAAzACAAKgAgAE4ARQApACAALwAgACgARwBFAEMAIAAqACAAawAgACoAIABxAG0AXwBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBJAF8AagA9AFwAXABmAHIAYQBjAHsATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFAH0AewBHAEUAQwBcAFwAdABpAG0AZQBzACAAawBcAFwAdABpAG0AZQBzACAAcQBtAF8AagB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARQBcACIALAAgAFwAIgBuAGUAdAAgAGUAbgBlAHIAZwB5AFwAIgAsACAAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBFAEMAXAAiACwAIABcACIAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAE0ASgAvAGsAZwBEAE0AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBrAFwAIgAsACAAXAAiAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBtAF8AagBcACIALAAgAFwAIgBtAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAdABoAGUAIABkAGkAZQB0AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADYAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4ATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXABuAE0AUABfAGoAXABuAEwALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AUABfAGoAPQBNAFMAXwBqAC8AKAAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAKQBcAG4ATQBTAF8AagAgAD0AIABkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAKABrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARgBDAF8AagAgAD0AIABmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAFAAQwBfAGoAIAA9ACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBTAF8AagAsACAARgBDAF8AagAsACAAUABDAF8AagAsAFwAbgAgACAAIAAgAE0AUwBfAGoAIAAvACAAKAAwAC4AMAAxACAAKgAgACgARgBDAF8AagAgACsAIABQAEMAXwBqACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUABfAGoAPQBcAFwAZgByAGEAYwB7AE0AUwBfAGoAfQB7ADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXwBNAGUAdABoAG8AZAAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFMAXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBDAF8AagBcACIALAAgAFwAIgBmAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEMAXwBqAFwAIgAsACAAXAAiAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgAgAEMAbwBuAHYAZQByAHQAZQBkACAAaQBuAHAAdQB0ACAARgBDACAAYQBuAGQAIABQAEMAIABwAGUAcgBjAGUAbgB0ACAAdABvACAAaQBuAHQAZQBnAGUAcgAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAbgBxAG0AXwBqAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4ANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgAwADAANwA5ADUAIAAqACAAKABEAE0ARABfAGoAIAAqACAAMQAwADAAKQAgAC0AIAAwAC4AMAAwADEANABcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4ANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgAwADAANwA5ADUAXABcAHQAaQBtAGUAcwAgACgARABNAEQAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAMAApAC0AMAAuADAAMAAxADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBEAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGUAeABwAHIAZQBzAHMAZQBkACAAYQBzACAAYQAgAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAYwBoAGEAbgBnAGUAZAAgADAALgA3ADkANQAgAHQAbwAgADAALgAwADAANwA5ADUAIAB3AGgAaQBjAGgAIABpAHMAIAB0AGgAZQAgAHYAYQBsAHUAZQAgAHUAcwBlAGQAIABpAG4AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIAQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALAAgAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4ALQAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAqAEYAcgBhAGMAdABpAG8AbgBTAGUAcABhAHIAYQB0AGUAZAApACkAXABuACkAOwBcAG4AXABuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4ALABcAG4AIAAgACAAIABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAFwAbgAgACAAIAAgACAAIAAgACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMQBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMgBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACgATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4AIAAqACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAApAFwAbgAgACAAIAAgACkAXABuACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24877,12 +24912,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFwAIgAgACYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABDAG8AdwBzACAAYQBuAGQAIABIAGUAaQBmAGUAcgBzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgACcAUgBlAGYAZQByAGUAbgBjAGUAJwAsACAAYQBzACAAdABoAGUAIAB2AGEAbAB1AGUAIABpAHMAIABjAG8AbgBzAGkAcwB0AGUAbgB0AGwAeQAgACcARABhAGkAcgB5ACAAQQB1AHMAdAByAGEAbABpAGEAIABbADEAXQAnACAAYQBuAGQAIABpAHMAIABuAG8AdAAgAHUAcwBlAGQAIABpAG4AIABjAGEAbABjAHUAbABhAHQAaQBvAG4ALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHIAZQBlAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAZABpAHUAbQAgAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADUANQAwACwAIAAzADgAMAAsACAAMQA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABhAHIAZwBlACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AbABzAHQAZQBpAG4ALQBGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADUAMAAsACAANAA1ADAALAAgADEAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBpAGUAcwBpAGEAbgAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANQAwADAALAAgADMANQAwACwAIAAxADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQBcACIALAAgADQAMAAwACwAIAAyADcANQAsACAAMQAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBlAHIAcwBlAHkAIABjAHIAbwBzAHMAYgByAGUAZABcACIALAAgADQANQAwACwAIAAzADEANQAsACAAMQAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB5AHIAcwBoAGkAcgBlAFwAIgAsACAANQA0ADAALAAgADMANwA1ACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHUAZQByAG4AcwBlAHkAXAAiACwAIAA0ADgAMAAsACAAMwAzADUALAAgADEANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBvAHcAbgAgAFMAdwBpAHMAcwBcACIALAAgADYAMAAwACwAIAA0ADEANQAsACAAMQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBsAGwAYQB3AGEAcgByAGEALwBBAHUAcwBzAGkAZQAgAFIAZQBkAFwAIgAsACAANQA1ADAALAAgADMANwA1ACwAIAAxADUAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEIAdQBsAGwAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBCAHUAbABsAHMAIAA+ADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAGIAcgBlAGUAZABzAFwAIgAsACAANgAwADAALAAgADIAMgA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnACkAIAAoAEwAVwBHAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnACkAIAAoAEwAVwBHAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABXAEcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAANQA5ADAALAAgADUAOQAwACwAIAA1ADkAMAAsACAANwA3ADAALAAgADcANwAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAD0AMwAsADUAOwAgAE4AUABXAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAJwBBAG4AaQBtAGEAbAAgAGMAbABhAHMAcwAgAGoAJwAgAGMAbwBsAHUAbQBuACAAaABlAGEAZABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAYwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAAoAFYAUwBqAD0AMwAsADUAKQBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIABFAHgAYwByAGUAdABlAGQAIAAoAE4AUABXAGoAPQAzACwANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwA8ADEAXAAiACwAIAAwAC4AMAAxADcANgAsACAAMAAuADIANgA4ADUALAAgADAALgAwADEAMwA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwA8ADEAXAAiACwAIAAwAC4AMAAyADAANAAsACAAMAAuADMAMAAwADMALAAgADAALgAwADAAOQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADYAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBqAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADYAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBqAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEMARgBqAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAAnAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADEAMAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAMAAuADcAMgAsACAAMAAuADcANgAsACAAMAAuADgALAAgADAALgA3ADgALAAgADAALgA3ADQALAAgADAALgA2ADkALAAgADAALgA3ADMALAAgADAALgA3ADYALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAcwAgACgAYQApAFwAIgAsACAAMAAuADEANQAsACAAMAAuADEAOAAsACAAMAAuADUAMAAsACAAMAAuADIANAAsACAAMAAuADEANwAsACAAMAAuADEAMwAsACAAMAAuADEANwAsACAAMAAuADEAOAAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AOwAgAEYAcgBhAGMARwBBAFMATQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkACkAXAAiACwAIABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQA0ACAAUABhAHMAdAB1AHIAZQBcACIALAAgADAALAAgADAALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMQAgAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIAAwACwAIAAwAC4AMwA1ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQA9ADIAIABEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgADAALgAwADcALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAEQAcgBhAGkAbgBzACAAdABvACAAUABhAGQAZABvAGMAawBcACIALAAgADAALAAgADAALgAyACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMwAgAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAzACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA4ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAIAAoAE0AUABXAEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEMAbABhAHMAcwAgAGoAXAAiACwAIABcACIATQBQAFcARQBOAFQARQBSAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABlAGkAZgBlAHIAcwAgADwAIAAxACAAeQBlAGEAcgBcACIALAAgADAALgAwADEANwA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgADwAIAAxACAAeQBlAGEAcgBcACIALAAgADAALgAwADIAMAA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA5ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABJAG4AYwByAGUAYQBzAGUAZAAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApACAAKABNAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADkAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEkAbgBjAHIAZQBhAHMAZQBkACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawAgACgATQBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABDAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAE0AUgBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAYwBvAHcAcwAsACAAYQBuAGQAIABoAG8AdQBzAGUAIABjAG8AdwBzAFwAIgAsACAAMQAuADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwBlAHMAXAAiACwAIAAxAC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB2AG8AaQBkAGUAZAAgAHQAbwAgAGUAYQBjAGgAIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAIABzAHkAcwB0AGUAbQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0ATQBTAGoAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADAAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdgBvAGkAZABlAGQAIAB0AG8AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAE0AUwBqAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAGoAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAJwBBAG4AbgB1AGEAbAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaQBtAGUAIABzAHAAZQBuAHQAIABwAGUAcgAgAGEAcgBlAGEAJwAgAHIAbwB3ACAAYQBzACAAdABoAGkAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGkAcwAgAGkAbgAgAHQAaABlACAAdABhAGIAbABlACAAdABpAHQAbABlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQByAGUAYQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABTAGgAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAcABhAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMQA6ACAARwByAGEAegBlAGQAIABPAG4AbAB5AFwAIgAsACAAMAAuADgAOQAsACAAMAAuADEAMQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADIAOgAgAE8AbgAgAGYAZQBlAGQAcABhAGQAIABmAG8AcgAgADwAMQAwACAAaAByAC8AZABhAHkAIABmAG8AcgAgADwAMwAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA3ADkALAAgADAALgAxADEALAAgADAALgAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAAzADoAIABQAGEAcwB0AHUAcgBlAC0AZwByAGEAegBlAGQAIAAzAC0AOQAgAG0AbwBuAHQAaABzAC8AeQBlAGEAcgBcACIALAAgADAALgA1ADMANAAsACAAMAAuADEAMQAsACAAMAAuADMANQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAANAA6ACAAWgBlAHIAbwAgAGcAcgBhAHoAaQBuAGcAXAAiACwAIAAwACwAIAAwAC4AMQAxACwAIAAwAC4AOAA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEUARgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAZQByACAATQBNAFMAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAAnAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBFAEYAbQBcACIALAAgAFwAIgBOAEkAUgAgAHIAZQBmAGUAcgBlAG4AYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMQA0ACAAUABhAHMAdAB1AHIAZQBcACIALAAgADAALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMQAgAEEAbgBlAHIAbwBiAGkAYwAgAEwAYQBnAG8AbwBuAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAyACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzAFwAIgAsACAAMAAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADQAIABTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAMAAuADAAMAA1ACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBcAG4ARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuAHAAdQB0ACAAYwBsAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgBwAHUAdAAgAGMAbABhAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAYQB5AHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEMAbwBuAHYAZQByAHQAZQBkACAAZgByAGUAZQAgAHQAZQB4AHQAIABpAG4AIABkAG8AYwB1AG0AZQBuAHQAIAB0AG8AIAB0AGEAYgBsAGUALAAgAG0AYQB0AGMAaABpAG4AZwAgAGwAaQB2AGUAcwB0AG8AYwBrACAAYwBsAGEAcwBzACAAbgBhAG0AZQBzAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAGMAbABhAHMAcwAgAGoAXAAiACwAIABcACIARAB1AHIAYQB0AGkAbwBuACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEQAdQByAGEAdABpAG8AbgAgACgAcAByAGUALQB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAYwBvAHcAcwBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIAA+ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAgADEAIAB5AGUAYQByAFwAIgAsACAAMgA4ADEALAAgADgANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIAA+ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIAA8ACAAMQAgAHkAZQBhAHIAXAAiACwAIAAyADgAMQAsACAAOAA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAFwAbgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAUABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQATQBEAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgBcAHQARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA3ADUAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBcAG4ATgBlAHQAIABlAG4AZQByAGcAeQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAEUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAvACAAawBnACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAwADUANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AFwAbgBHAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAZAByAHkAIABtAGEAdAB0AGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcARQBDAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEoAIAAvACAAawBnAEQATQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADEAOAAuADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBcAG4ARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIAB1AHMAZQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYAMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAOAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAXwBvAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMQAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5ACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgBvAHIAIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAATQBNAFMAIABvAG4AbAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARABlAGYAYQB1AGwAdAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAdwBoAGUAbgAgAG0AYQBuAHUAcgBlACAAaQBzACAAZQB4AGMAcgBlAHQAZQBkACAAdABvACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAKABtAD0AMQA0ACkALgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBfAEwARQBBAEMASABfAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAegBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAMQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXABuAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAdAAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMgAgAEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0AC4AMAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4AUAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAEMAXwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcABlAHIAYwBlAG4AdABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAzAC4AMwApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADMAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABEAGEAaQByAHkAIABDAGEAdAB0AGwAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9ACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ATgBfAGoAMQAyADQAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADEAMgA0ACAAPQAgAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADEAMgA0ACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0ACAAKABkAGEAeQBzACkAXABuAE4AXwBqADMANQAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAaABlAGEAZAApAFwAbgBNAF8AagAzADUAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBEAF8AagAzADUAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQAgACgAZABhAHkAcwApAFwAbgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AagAxADIANAAsACAATQBfAGoAMQAyADQALAAgAEQAXwBqADEAMgA0ACwAIABOAF8AagAzADUALAAgAE0AXwBqADMANQAsACAARABfAGoAMwA1ACwAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAsAFwAbgAgACAAIAAgACgAKABOAF8AagAxADIANAAgACoAIABNAF8AagAxADIANAAgACoAIABEAF8AagAxADIANAApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AXwBqADMANQAgACoAIABEAF8AagAzADUAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQAgACoAIABEAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAEQAUABXAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAUABXAF8AagAzADUAKQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABQAFcAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAxADIANABcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqADEAMgA0AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMQAsADIALAA0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagAzADUAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHcAZQBhAG4AZQBkACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABQAFcAXwBqADMANQBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAXAAiACwAIABcACIAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgACcARABQAFcAJwAgAHYAYQByAGkAYQBiAGwAZQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGgAYQBuAGQAbABpAG4AZwAgAG8AZgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABkAHUAcgBhAHQAaQBvAG4ALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcAG4ATQBfAGoAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AagA9ADIAMAAuADcAXABcAHQAaQBtAGUAcwAgAEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAXABuACAAIAAgACAAMgAwAC4ANwAgACoAIABJAF8AagAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAaABhAHIAbQBsAGUAeQAgAGUAdAAgAGEAbAAuACAAKAAyADAAMQA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagA9ADIAMAAuADcAXABcAHQAaQBtAGUAcwAgAEkAXwBqAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAFwAbgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXABuAEkAXwBqAFwAbgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEkAXwBqAD0AKAAxAC4AMQA4ADUAKwAwAC4AMAAwADQANQA0AFwAXAB0AGkAbQBlAHMAIABXAF8AagAtADAALgAwADAAMAAwADAAMgA2AFwAXAB0AGkAbQBlAHMAIABXAF8AagBeADIAKwAwAC4AMwAxADUAXABcAHQAaQBtAGUAcwAgAEwAVwBHAF8AagApAF4AMgBcAFwAdABpAG0AZQBzACAATQBSAF8AagArAE0ASQBfAGoAXABuAFcAXwBqACAAPQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApAFwAbgBMAFcARwBfAGoAIAA9ACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIAAoAGsAZwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBNAFIAXwBqACAAPQAgAGkAbgBjAHIAZQBhAHMAZQAgAGkAbgAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgBNAEkAXwBqACAAPQAgAGEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwBqACwAIABMAFcARwBfAGoALAAgAE0AUgBfAGoALAAgAE0ASQBfAGoALABcAG4AIAAgACAAIAAoADEALgAxADgANQAgACsAIAAwAC4AMAAwADQANQA0ACAAKgAgAFcAXwBqACAALQAgADAALgAwADAAMAAwADAAMgA2ACAAKgAgAFcAXwBqACAAXgAgADIAIAArACAAMAAuADMAMQA1ACAAKgAgAEwAVwBHAF8AagApACAAXgAgADIAIAAqACAATQBSAF8AagAgACsAIABNAEkAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAXwBqAD0AKAAxAC4AMQA4ADUAKwAwAC4AMAAwADQANQA0AFwAXAB0AGkAbQBlAHMAIABXAF8AagAtADAALgAwADAAMAAwADAAMgA2AFwAXAB0AGkAbQBlAHMAIABXAF8AagBeADIAKwAwAC4AMwAxADUAXABcAHQAaQBtAGUAcwAgAEwAVwBHAF8AagApAF4AMgBcAFwAdABpAG0AZQBzACAATQBSAF8AagArAE0ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBqAFwAIgAsACAAXAAiAGwAaQB2AGUAdwBlAGkAZwBoAHQAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABXAEcAXwBqAFwAIgAsACAAXAAiAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUgBfAGoAXAAiACwAIABcACIAaQBuAGMAcgBlAGEAcwBlACAAaQBuACAAbQBlAHQAYQBiAG8AbABpAGMAIAByAGEAdABlACAAdwBoAGUAbgAgAHAAcgBvAGQAdQBjAGkAbgBnACAAbQBpAGwAawBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEkAXwBqAFwAIgAsACAAXAAiAGEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ATQBJAF8AagBcAG4AawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAEkAXwBqAD0AKABNAFAAXwBqAFwAXAB0AGkAbQBlAHMAIAAxAC4AMAAzAFwAXAB0AGkAbQBlAHMAIABOAEUAKQAvACgARwBFAEMAXABcAHQAaQBtAGUAcwAgAGsAXABcAHQAaQBtAGUAcwAgAHEAbQBfAGoAKQBcAG4ATQBQAF8AagAgAD0AIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgATAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBOAEUAIAA9ACAAbgBlAHQAIABlAG4AZQByAGcAeQAgACgATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAvAGsAZwAgAG0AaQBsAGsAKQBcAG4ARwBFAEMAIAA9ACAAZwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAKABNAEoALwBrAGcARABNACkAXABuAGsAIAA9ACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAHUAcwBlACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAHEAbQBfAGoAIAA9ACAAbQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAHQAaABlACAAZABpAGUAdAAgACgAZgByAGEAYwB0AGkAbwBuACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AUABfAGoALAAgAE4ARQAsACAARwBFAEMALAAgAGsALAAgAHEAbQBfAGoALABcAG4AIAAgACAAIAAoAE0AUABfAGoAIAAqACAAMQAuADAAMwAgACoAIABOAEUAKQAgAC8AIAAoAEcARQBDACAAKgAgAGsAIAAqACAAcQBtAF8AagApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASQBfAGoAPQBcAFwAZgByAGEAYwB7AE0AUABfAGoAXABcAHQAaQBtAGUAcwAgADEALgAwADMAXABcAHQAaQBtAGUAcwAgAE4ARQB9AHsARwBFAEMAXABcAHQAaQBtAGUAcwAgAGsAXABcAHQAaQBtAGUAcwAgAHEAbQBfAGoAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABVAFwAIgAsACAAXAAiAGkAbgBwAHUAdAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABfAGoAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGkAZgAgAGkAbgBwAHUAdAAgAGEAcwAgAGwAaQB0AHIAZQBzACAAbwBmACAAbQBpAGwAawApAFwAIgAsACAAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAXwBqAFwAIgAsACAAXAAiAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABpAGYAIABpAG4AcAB1AHQAIABhAHMAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAKQBcACIALAAgAFwAIgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEUAXAAiACwAIABcACIAbgBlAHQAIABlAG4AZQByAGcAeQBcACIALAAgAFwAIgBNAEoAIABuAGUAdAAgAGUAbgBlAHIAZwB5AC8AawBnACAAbQBpAGwAawBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcARQBDAFwAIgAsACAAXAAiAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdABcACIALAAgAFwAIgBNAEoALwBrAGcARABNAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAawBcACIALAAgAFwAIgBlAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAdQBzAGUAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAbQBfAGoAXAAiACwAIABcACIAbQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAHQAaABlACAAZABpAGUAdABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAAzAC4AMwAuADEALgAxACAAKAA2ACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAdQBzAGUAIABvAGYAIABlAGkAdABoAGUAcgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwAgAG8AcgAgAGwAaQB0AHIAZQBzACAAbwBmACAAbQBpAGwAawAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXABuAE0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAYwBvAG4AdgBlAHIAdABlAGQAIABmAHIAbwBtACAAbQBpAGwAawAgAHMAbwBsAGkAZABzAFwAbgBNAFAAXwBqAFwAbgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAFAAXwBqAD0ATQBTAF8AagAvACgAMAAuADAAMQBcAFwAdABpAG0AZQBzACAAKABGAEMAXwBqACsAUABDAF8AagApACkAXABuAE0AUwBfAGoAIAA9ACAAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwAgACgAawBnACAATQBTAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEYAQwBfAGoAIAA9ACAAZgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgBQAEMAXwBqACAAPQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AUwBfAGoALAAgAEYAQwBfAGoALAAgAFAAQwBfAGoALABcAG4AIAAgACAAIABNAFMAXwBqACAALwAgACgAMAAuADAAMQAgACoAIAAoAEYAQwBfAGoAIAArACAAUABDAF8AagApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABjAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBvAG0AIABtAGkAbABrACAAcwBvAGwAaQBkAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAXwBqAD0AXABcAGYAcgBhAGMAewBNAFMAXwBqAH0AewAwAC4AMAAxAFwAXAB0AGkAbQBlAHMAIAAoAEYAQwBfAGoAKwBQAEMAXwBqACkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAaQBuAHAAdQB0ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBTAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzAFwAIgAsACAAXAAiAGsAZwAgAE0AUwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAQwBfAGoAXAAiACwAIABcACIAZgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABDAF8AagBcACIALAAgAFwAIgBwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAFUAXAAiACwAIABcACIAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBTAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBpAGwAawAgAHMAbwBsAGkAZABzAFwAIgAsACAAXAAiAGsAZwAgAE0AUwAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAQwBfAGoAXAAiACwAIABcACIAZgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABDAF8AagBcACIALAAgAFwAIgBwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAB1AG4AaQB0ACAAdgBhAHIAaQBhAGIAbABlACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIAB1AHMAZQAgAG8AZgAgAGUAaQB0AGgAZQByACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACAAbwByACAAbABpAHQAcgBlAHMAIABvAGYAIABtAGkAbABrAC4AIABDAG8AbgB2AGUAcgB0AGUAZAAgAGkAbgBwAHUAdAAgAEYAQwAgAGEAbgBkACAAUABDACAAcABlAHIAYwBlAG4AdAAgAHQAbwAgAGkAbgB0AGUAZwBlAHIALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFwAbgBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAZABpAGUAdABcAG4AcQBtAF8AagBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBxAG0AXwBqAD0AMAAuADcAOQA1AFwAXAB0AGkAbQBlAHMAIAAoAEQATQBEAF8AagBcAFwAdABpAG0AZQBzACAAMQAwADAAKQAtADAALgAwADAAMQA0AFwAbgBEAE0ARABfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABNAEQAXwBqACwAXABuACAAIAAgACAAMAAuADcAOQA1ACAAKgAgACgARABNAEQAXwBqACAAKgAgADEAMAAwACkAIAAtACAAMAAuADAAMAAxADQAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAE0ARABfAGoALABcAG4AIAAgACAAIAAwAC4AMAAwADcAOQA1ACAAKgAgACgARABNAEQAXwBqACAAKgAgADEAMAAwACkAIAAtACAAMAAuADAAMAAxADQAXABuACAAIAApADsAXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIABkAGkAZQB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAD0AMAAuADcAOQA1AFwAXAB0AGkAbQBlAHMAIAAoAEQATQBEAF8AagBcAFwAdABpAG0AZQBzACAAMQAwADAAKQAtADAALgAwADAAMQA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAPQAwAC4AMAAwADcAOQA1AFwAXAB0AGkAbQBlAHMAIAAoAEQATQBEAF8AagBcAFwAdABpAG0AZQBzACAAMQAwADAAKQAtADAALgAwADAAMQA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0ARABfAGoAXAAiACwAIABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAGMAaABhAG4AZwBlAGQAIAAwAC4ANwA5ADUAIAB0AG8AIAAwAC4AMAAwADcAOQA1ACAAdwBoAGkAYwBoACAAaQBzACAAdABoAGUAIAB2AGEAbAB1AGUAIAB1AHMAZQBkACAAaQBuACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0AFwAIgApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4ATQBNAFMAQQBmAHQAZQByAFMAbwBsAGkAZABTAGUAcABhAHIAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAATQBNAFMARgByAGEAYwB0AGkAbwBuACwAIABGAHIAYQBjAHQAaQBvAG4AUwBlAHAAYQByAGEAdABlAGQALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACAAKgAgACgATQBNAFMARgByAGEAYwB0AGkAbwBuAC0AKABNAE0AUwBGAHIAYQBjAHQAaQBvAG4AKgBGAHIAYQBjAHQAaQBvAG4AUwBlAHAAYQByAGEAdABlAGQAKQApAFwAbgApADsAXABuAFwAbgBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4ASQBuAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQBuAGkAdABhAGwAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUARgByAGEAYwB0AGkAbwBuACwAXABuACAAIAAgACAATQBNAFMAMQBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADEAUwBlAHAAYQByAGEAdABlAGQALAAgAFwAbgAgACAAIAAgAE0ATQBTADIARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAyAFMAZQBwAGEAcgBhAHQAZQBkACwAIABcAG4AIAAgACAAIABNAE0AUwAzAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMwBTAGUAcABhAHIAYQB0AGUAZAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AIAAqACAAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAbgBpAHQAYQBsAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAEYAcgBhAGMAdABpAG8AbgAgACsAXABuACAAIAAgACAAIAAgACAAIAAoAE0ATQBTADEARgByAGEAYwB0AGkAbwBuACAAKgAgAE0ATQBTADEAUwBlAHAAYQByAGEAdABlAGQAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAoAE0ATQBTADIARgByAGEAYwB0AGkAbwBuACAAKgAgAE0ATQBTADIAUwBlAHAAYQByAGEAdABlAGQAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAoAE0ATQBTADMARgByAGEAYwB0AGkAbwBuACAAKgAgAE0ATQBTADMAUwBlAHAAYQByAGEAdABlAGQAKQBcAG4AIAAgACAAIAApAFwAbgApADsAIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEIAZQBlAGYAQwBhAHQAdABsAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEIAZQBlAGYAQwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEIAZQBlAGYAQwBhAHQAdABsAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEIAZQBlAGYAQwBhAHQAdABsAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzAF8ATQBlAHQAaABvAGQAMgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdAAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBNAE0AUwBBAGYAdABlAHIAUwBvAGwAaQBkAFMAZQBwAGEAcgBhAHQAaQBvAG4AIgAsACIASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAF8ARABhAGkAcgB5AC4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24897,9 +24927,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24924,9 +24954,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59C64C6-9746-403D-A9DA-6885C9D0B99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8E1175-DAC7-445C-B4CE-C6F8D5E42A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="1065" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="2" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -182,6 +182,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateFractionResidueRemoved">_xlfn.LAMBDA(_xlpm.TotalResidue,_xlpm.AmountRemoved, (_xlpm.AmountRemoved * 10 ^ 3) / (_xlpm.TotalResidue * 10 ^ 3))</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateHarvestIndex">_xlfn.LAMBDA(_xlpm.CropType,_xlpm.CropTypeArray,_xlpm.ResidueCropRatioArray, 1 / (1 + Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.CropType, _xlpm.CropTypeArray, _xlpm.ResidueCropRatioArray)))</definedName>
     <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateResidueCropRatio">_xlfn.LAMBDA(_xlpm.HarvestIndex, (1 - _xlpm.HarvestIndex) / _xlpm.HarvestIndex)</definedName>
@@ -497,6 +498,18 @@
     <definedName name="SourceData_Dairy.SourceData_Dairy_ReferenceWeights_Unit">_xlfn.LAMBDA("kg")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_ReferenceWeights_Variable">_xlfn.LAMBDA("WRj")</definedName>
     <definedName name="SourceData_Dairy.SourceData_Dairy_ReferenceWeights_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_Dairy_AshContent_Data">'Constants - Dairy'!$D$188</definedName>
+    <definedName name="SourceData_Dairy_CrudeProtein_Data">'Constants - Dairy'!$D$153</definedName>
+    <definedName name="SourceData_Dairy_DryMatterDigestibility_Data">'Constants - Dairy'!$D$160</definedName>
+    <definedName name="SourceData_Dairy_EfficiencyOfUseOfMetabolizableEnergy_Data">'Constants - Dairy'!$D$181</definedName>
+    <definedName name="SourceData_Dairy_EmissionFactorForLeachingAndRunoff_Data">'Constants - Dairy'!$D$202</definedName>
+    <definedName name="SourceData_Dairy_FatContentInMilk_Data">'Constants - Dairy'!$D$221</definedName>
+    <definedName name="SourceData_Dairy_FracGASMSoil_Data">'Constants - Dairy'!$D$215</definedName>
+    <definedName name="SourceData_Dairy_FractionOfNitrogenLostThroughLeachingAndRunoff_Data">'Constants - Dairy'!$D$209</definedName>
+    <definedName name="SourceData_Dairy_GrossEnergyContent_Data">'Constants - Dairy'!$D$174</definedName>
+    <definedName name="SourceData_Dairy_MethaneEmissionsPotential_Data">'Constants - Dairy'!$D$195</definedName>
+    <definedName name="SourceData_Dairy_NetEnergy_Data">'Constants - Dairy'!$D$167</definedName>
+    <definedName name="SourceData_Dairy_ProteinContentInMilk_Data">'Constants - Dairy'!$D$227</definedName>
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
@@ -14556,23 +14569,23 @@
         <v>16</v>
       </c>
       <c r="E36" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="F36" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="G36" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="H36" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="I36" s="54">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -14588,23 +14601,23 @@
         <v>101</v>
       </c>
       <c r="E37" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="F37" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="G37" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="H37" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="I37" s="54">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -14648,23 +14661,23 @@
         <v>16</v>
       </c>
       <c r="E40" s="67">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="F40" s="67">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="G40" s="67">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="H40" s="67">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="I40" s="67">
-        <f>'Constants - Dairy'!$D$160</f>
+        <f>SourceData_Dairy_DryMatterDigestibility_Data</f>
         <v>0.75</v>
       </c>
       <c r="J40" s="2" t="s">
@@ -14679,23 +14692,23 @@
         <v>101</v>
       </c>
       <c r="E41" s="67">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="F41" s="67">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="G41" s="67">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="H41" s="67">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="I41" s="67">
-        <f>'Constants - Dairy'!$D$153</f>
+        <f>SourceData_Dairy_CrudeProtein_Data</f>
         <v>0.2</v>
       </c>
       <c r="J41" s="2" t="s">
@@ -14825,11 +14838,11 @@
         <v>242</v>
       </c>
       <c r="E55" s="124">
-        <f>'Constants - Dairy'!$D$221/100</f>
+        <f>SourceData_Dairy_FatContentInMilk_Data/100</f>
         <v>0.04</v>
       </c>
       <c r="F55" s="132">
-        <f>'Constants - Dairy'!$D$221/100</f>
+        <f>SourceData_Dairy_FatContentInMilk_Data/100</f>
         <v>0.04</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -14842,11 +14855,11 @@
         <v>243</v>
       </c>
       <c r="E56" s="124">
-        <f>'Constants - Dairy'!$D$227/100</f>
+        <f>SourceData_Dairy_ProteinContentInMilk_Data/100</f>
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="F56" s="132">
-        <f>'Constants - Dairy'!$D$227/100</f>
+        <f>SourceData_Dairy_ProteinContentInMilk_Data/100</f>
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -16050,7 +16063,7 @@
         <v>Constant</v>
       </c>
       <c r="I67" s="122">
-        <f>'Constants - Dairy'!$D$167</f>
+        <f>SourceData_Dairy_NetEnergy_Data</f>
         <v>3.0539999999999998</v>
       </c>
     </row>
@@ -16069,7 +16082,7 @@
         <v>Constant</v>
       </c>
       <c r="I68" s="122">
-        <f>'Constants - Dairy'!$D$174</f>
+        <f>SourceData_Dairy_GrossEnergyContent_Data</f>
         <v>18.399999999999999</v>
       </c>
     </row>
@@ -16088,7 +16101,7 @@
         <v>Constant</v>
       </c>
       <c r="I69" s="122">
-        <f>'Constants - Dairy'!$D$181</f>
+        <f>SourceData_Dairy_EfficiencyOfUseOfMetabolizableEnergy_Data</f>
         <v>0.6</v>
       </c>
     </row>
@@ -24708,12 +24721,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAPAB0AD4APABzAD4AXAAiACAAJgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgA8AC8AcwA+ADwAcwA+AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAXAAiADwALwBzAD4APAAvAHQAPgBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAD4APQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApADwAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAD4APQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApADwAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQA+AD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQA8AD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAD4APQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAPAA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQA+AD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAPAA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAD4APQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApADwAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AJwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPABTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAD4ARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAD4AMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAJwBcACIAIAAmACAAcwBoACAAJgAgAFwAIgAnACEAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAJgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAJgAgAFwAIgAgAFwAIgAgACYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAxAC8AKAAxACsAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACwAXABuACAAIAAgACAAKAAxAC0ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAKQAvAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACwAIABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACwAXABuACAAIAAgACAAKABBAG0AbwB1AG4AdABSAGUAbQBvAHYAZQBkACoAMQAwAF4AMwApAC8AKABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAqADEAMABeADMAKQBcAG4AKQAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABDAG8AdwBzACAAYQBuAGQAIABIAGUAaQBmAGUAcgBzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgACcAUgBlAGYAZQByAGUAbgBjAGUAJwAsACAAYQBzACAAdABoAGUAIAB2AGEAbAB1AGUAIABpAHMAIABjAG8AbgBzAGkAcwB0AGUAbgB0AGwAeQAgACcARABhAGkAcgB5ACAAQQB1AHMAdAByAGEAbABpAGEAIABbADEAXQAnACAAYQBuAGQAIABpAHMAIABuAG8AdAAgAHUAcwBlAGQAIABpAG4AIABjAGEAbABjAHUAbABhAHQAaQBvAG4ALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHIAZQBlAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAZABpAHUAbQAgAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADUANQAwACwAIAAzADgAMAAsACAAMQA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABhAHIAZwBlACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AbABzAHQAZQBpAG4ALQBGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADUAMAAsACAANAA1ADAALAAgADEAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBpAGUAcwBpAGEAbgAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANQAwADAALAAgADMANQAwACwAIAAxADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQBcACIALAAgADQAMAAwACwAIAAyADcANQAsACAAMQAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBlAHIAcwBlAHkAIABjAHIAbwBzAHMAYgByAGUAZABcACIALAAgADQANQAwACwAIAAzADEANQAsACAAMQAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB5AHIAcwBoAGkAcgBlAFwAIgAsACAANQA0ADAALAAgADMANwA1ACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHUAZQByAG4AcwBlAHkAXAAiACwAIAA0ADgAMAAsACAAMwAzADUALAAgADEANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBvAHcAbgAgAFMAdwBpAHMAcwBcACIALAAgADYAMAAwACwAIAA0ADEANQAsACAAMQA3ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBsAGwAYQB3AGEAcgByAGEALwBBAHUAcwBzAGkAZQAgAFIAZQBkAFwAIgAsACAANQA1ADAALAAgADMANwA1ACwAIAAxADUAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEIAdQBsAGwAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAcgBlAGUAZABcACIALAAgAFwAIgBCAHUAbABsAHMAIAA+ADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAGIAcgBlAGUAZABzAFwAIgAsACAANgAwADAALAAgADIAMgA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnACkAIAAoAEwAVwBHAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnACkAIAAoAEwAVwBHAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABXAEcAagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIAA8ADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4ANAA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAAUgBlAGYAZQByAGUAbgBjAGUAIAB3AGUAaQBnAGgAdABzACAAKABrAGcAKQAgACgAVwBSAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFcAUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4ANABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADUALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAD4AMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAPAAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAD4AMQBcACIALAAgAFw